--- a/datasets/sheet1.xlsx
+++ b/datasets/sheet1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="149">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -91,6 +91,9 @@
     <t>주요제품</t>
   </si>
   <si>
+    <t>2024-07-23</t>
+  </si>
+  <si>
     <t>2024-07-15</t>
   </si>
   <si>
@@ -139,6 +142,9 @@
     <t>2024-05-23</t>
   </si>
   <si>
+    <t>2024-07-29</t>
+  </si>
+  <si>
     <t>2024-07-19</t>
   </si>
   <si>
@@ -163,15 +169,15 @@
     <t>2024-05-29</t>
   </si>
   <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
     <t>2024-08-06</t>
   </si>
   <si>
     <t>2024-07-26</t>
   </si>
   <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
     <t>2024-07-12</t>
   </si>
   <si>
@@ -199,6 +205,9 @@
     <t>2024-07-01</t>
   </si>
   <si>
+    <t>미래</t>
+  </si>
+  <si>
     <t>삼성</t>
   </si>
   <si>
@@ -217,9 +226,6 @@
     <t>엘에스</t>
   </si>
   <si>
-    <t>미래</t>
-  </si>
-  <si>
     <t>한국</t>
   </si>
   <si>
@@ -235,6 +241,9 @@
     <t>신한, 한국</t>
   </si>
   <si>
+    <t>뱅크웨어글로벌</t>
+  </si>
+  <si>
     <t>아이빔테크놀로지</t>
   </si>
   <si>
@@ -298,6 +307,9 @@
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
+    <t>155.74:1</t>
+  </si>
+  <si>
     <t>1011.50:1</t>
   </si>
   <si>
@@ -361,6 +373,9 @@
     <t>38.7:1</t>
   </si>
   <si>
+    <t>1.52%</t>
+  </si>
+  <si>
     <t>0.49%</t>
   </si>
   <si>
@@ -395,6 +410,9 @@
   </si>
   <si>
     <t>0.95%</t>
+  </si>
+  <si>
+    <t>국내외 은행 및 금융기업 대상 코어뱅킹 소프트웨어</t>
   </si>
   <si>
     <t>생체현미경, CRO 서비스</t>
@@ -800,7 +818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y22"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -885,76 +903,76 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F2">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="G2">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J2">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K2">
-        <v>14965620</v>
+        <v>10000988</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="O2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="P2">
-        <v>1337894447</v>
+        <v>72895458363</v>
       </c>
       <c r="Q2">
-        <v>4495088983</v>
+        <v>72913766913</v>
       </c>
       <c r="R2">
-        <v>99398351</v>
+        <v>11230711680</v>
       </c>
       <c r="S2">
-        <v>-3330678562</v>
+        <v>-6524077412</v>
       </c>
       <c r="T2">
-        <v>-2905069801</v>
+        <v>-4556157069</v>
       </c>
       <c r="U2">
-        <v>-1314068310</v>
+        <v>-3633759729</v>
       </c>
       <c r="V2">
-        <v>-9735376868</v>
+        <v>-11528915410</v>
       </c>
       <c r="W2">
-        <v>-5043515600</v>
+        <v>-7978634776</v>
       </c>
       <c r="X2">
-        <v>-1257080998</v>
+        <v>-3801868433</v>
       </c>
       <c r="Y2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -962,76 +980,76 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="G3">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>14000</v>
+        <v>7300</v>
       </c>
       <c r="J3">
-        <v>17000</v>
+        <v>8500</v>
       </c>
       <c r="K3">
-        <v>6471740</v>
+        <v>14965620</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="N3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="O3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P3">
-        <v>5214628820</v>
+        <v>1337894447</v>
       </c>
       <c r="Q3">
-        <v>6009352447</v>
+        <v>4495088983</v>
       </c>
       <c r="R3">
-        <v>965797975</v>
+        <v>99398351</v>
       </c>
       <c r="S3">
-        <v>2015081728</v>
+        <v>-3330678562</v>
       </c>
       <c r="T3">
-        <v>1319755337</v>
+        <v>-2905069801</v>
       </c>
       <c r="U3">
-        <v>-44547594</v>
+        <v>-1314068310</v>
       </c>
       <c r="V3">
-        <v>1503069100</v>
+        <v>-9735376868</v>
       </c>
       <c r="W3">
-        <v>1410469786</v>
+        <v>-5043515600</v>
       </c>
       <c r="X3">
-        <v>24178632</v>
+        <v>-1257080998</v>
       </c>
       <c r="Y3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1039,99 +1057,99 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F4">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="G4">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>2000</v>
+        <v>14000</v>
       </c>
       <c r="J4">
-        <v>2000</v>
+        <v>17000</v>
       </c>
       <c r="K4">
-        <v>6345000</v>
+        <v>6471740</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>2000</v>
+        <v>22000</v>
       </c>
       <c r="N4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>5214628820</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>6009352447</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>965797975</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2015081728</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>1319755337</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>-44547594</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1503069100</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1410469786</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>24178632</v>
       </c>
       <c r="Y4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F5">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="G5">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1143,7 +1161,7 @@
         <v>2000</v>
       </c>
       <c r="K5">
-        <v>4420000</v>
+        <v>6345000</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1152,10 +1170,10 @@
         <v>2000</v>
       </c>
       <c r="N5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="O5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1185,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="Y5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1193,46 +1211,46 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F6">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="G6">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>6200</v>
+        <v>2000</v>
       </c>
       <c r="J6">
-        <v>7700</v>
+        <v>2000</v>
       </c>
       <c r="K6">
-        <v>10830212</v>
+        <v>4420000</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="O6" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1262,7 +1280,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1270,46 +1288,46 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F7">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="G7">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>2000</v>
+        <v>6200</v>
       </c>
       <c r="J7">
-        <v>2000</v>
+        <v>7700</v>
       </c>
       <c r="K7">
-        <v>5020000</v>
+        <v>10830212</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="N7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="O7" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1339,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1347,76 +1365,76 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F8">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="G8">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="J8">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="K8">
-        <v>7836009</v>
+        <v>5020000</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="O8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="P8">
-        <v>12596039842</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>14910346438</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>16039074617</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>1732604466</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2893667787</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>1613779678</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1558081149</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>2643467726</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>1795726428</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1424,76 +1442,76 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F9">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="G9">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>36400</v>
+        <v>9000</v>
       </c>
       <c r="J9">
-        <v>43300</v>
+        <v>12000</v>
       </c>
       <c r="K9">
-        <v>9375694</v>
+        <v>7836009</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="N9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="O9" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="P9">
-        <v>103267682</v>
+        <v>12596039842</v>
       </c>
       <c r="Q9">
-        <v>342201581</v>
+        <v>14910346438</v>
       </c>
       <c r="R9">
-        <v>231425455</v>
+        <v>16039074617</v>
       </c>
       <c r="S9">
-        <v>-7598692896</v>
+        <v>1732604466</v>
       </c>
       <c r="T9">
-        <v>-25822444575</v>
+        <v>2893667787</v>
       </c>
       <c r="U9">
-        <v>-15929213281</v>
+        <v>1613779678</v>
       </c>
       <c r="V9">
-        <v>-6973258680</v>
+        <v>1558081149</v>
       </c>
       <c r="W9">
-        <v>-48433907514</v>
+        <v>2643467726</v>
       </c>
       <c r="X9">
-        <v>-83246975113</v>
+        <v>1795726428</v>
       </c>
       <c r="Y9" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1501,76 +1519,76 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F10">
-        <v>3400000</v>
+        <v>1330000</v>
       </c>
       <c r="G10">
-        <v>3400000</v>
+        <v>1330000</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>4500</v>
+        <v>36400</v>
       </c>
       <c r="J10">
-        <v>5500</v>
+        <v>43300</v>
       </c>
       <c r="K10">
-        <v>30888000</v>
+        <v>9375694</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>7000</v>
+        <v>43300</v>
       </c>
       <c r="N10" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="P10">
-        <v>85187882584</v>
+        <v>103267682</v>
       </c>
       <c r="Q10">
-        <v>87525689695</v>
+        <v>342201581</v>
       </c>
       <c r="R10">
-        <v>77247394706</v>
+        <v>231425455</v>
       </c>
       <c r="S10">
-        <v>2205797752</v>
+        <v>-7598692896</v>
       </c>
       <c r="T10">
-        <v>4920387020</v>
+        <v>-25822444575</v>
       </c>
       <c r="U10">
-        <v>4336496285</v>
+        <v>-15929213281</v>
       </c>
       <c r="V10">
-        <v>1613954566</v>
+        <v>-6973258680</v>
       </c>
       <c r="W10">
-        <v>3980493669</v>
+        <v>-48433907514</v>
       </c>
       <c r="X10">
-        <v>2646634321</v>
+        <v>-83246975113</v>
       </c>
       <c r="Y10" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1581,73 +1599,73 @@
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F11">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="G11">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>2000</v>
+        <v>4500</v>
       </c>
       <c r="J11">
-        <v>2000</v>
+        <v>5500</v>
       </c>
       <c r="K11">
-        <v>6870000</v>
+        <v>30888000</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="N11" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="O11" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>85187882584</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>87525689695</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>77247394706</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2205797752</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>4920387020</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>4336496285</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1613954566</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>3980493669</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>2646634321</v>
       </c>
       <c r="Y11" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1655,43 +1673,43 @@
         <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F12">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="G12">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>7500</v>
+        <v>2000</v>
       </c>
       <c r="J12">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="K12">
-        <v>17529140</v>
+        <v>6870000</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>11500</v>
+        <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="O12" t="s">
         <v>122</v>
@@ -1724,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1732,46 +1750,46 @@
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F13">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="G13">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>2000</v>
+        <v>7500</v>
       </c>
       <c r="J13">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="K13">
-        <v>6930000</v>
+        <v>17529140</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>2000</v>
+        <v>11500</v>
       </c>
       <c r="N13" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="O13" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1801,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1809,22 +1827,22 @@
         <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F14">
-        <v>6000000</v>
+        <v>6450000</v>
       </c>
       <c r="G14">
-        <v>6000000</v>
+        <v>6450000</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1836,7 +1854,7 @@
         <v>2000</v>
       </c>
       <c r="K14">
-        <v>6220000</v>
+        <v>6930000</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1845,10 +1863,10 @@
         <v>2000</v>
       </c>
       <c r="N14" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="O14" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1878,30 +1896,30 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F15">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="G15">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -1913,7 +1931,7 @@
         <v>2000</v>
       </c>
       <c r="K15">
-        <v>4810000</v>
+        <v>6220000</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1922,10 +1940,10 @@
         <v>2000</v>
       </c>
       <c r="N15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="O15" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -1955,30 +1973,30 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F16">
-        <v>4750000</v>
+        <v>4000000</v>
       </c>
       <c r="G16">
-        <v>4750000</v>
+        <v>4000000</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -1990,7 +2008,7 @@
         <v>2000</v>
       </c>
       <c r="K16">
-        <v>5480000</v>
+        <v>4810000</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1999,10 +2017,10 @@
         <v>2000</v>
       </c>
       <c r="N16" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="O16" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -2032,84 +2050,84 @@
         <v>0</v>
       </c>
       <c r="Y16" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:25">
       <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" t="s">
         <v>37</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>47</v>
       </c>
-      <c r="C17" t="s">
-        <v>45</v>
-      </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F17">
-        <v>1300000</v>
+        <v>4750000</v>
       </c>
       <c r="G17">
-        <v>1300000</v>
+        <v>4750000</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>10500</v>
+        <v>2000</v>
       </c>
       <c r="J17">
-        <v>14000</v>
+        <v>2000</v>
       </c>
       <c r="K17">
-        <v>12293880</v>
+        <v>5480000</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>17000</v>
+        <v>2000</v>
       </c>
       <c r="N17" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="O17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P17">
-        <v>1386123525</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>1152944128</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>1885010467</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>-4388824706</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>-7990287699</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>-9803411085</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>-4430563401</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>-7988275689</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>-9916946238</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2117,230 +2135,230 @@
         <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
         <v>70</v>
       </c>
       <c r="E18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F18">
-        <v>1600000</v>
+        <v>1300000</v>
       </c>
       <c r="G18">
-        <v>1600000</v>
+        <v>1300000</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>20000</v>
+        <v>10500</v>
       </c>
       <c r="J18">
-        <v>23500</v>
+        <v>14000</v>
       </c>
       <c r="K18">
-        <v>8751446</v>
+        <v>12293880</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>30000</v>
+        <v>17000</v>
       </c>
       <c r="N18" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O18" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>1386123525</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>1152944128</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1885010467</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>-4388824706</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>-7990287699</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>-9803411085</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>-4430563401</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>-7988275689</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>-9916946238</v>
       </c>
       <c r="Y18" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:25">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F19">
-        <v>1298000</v>
+        <v>1600000</v>
       </c>
       <c r="G19">
-        <v>1298000</v>
+        <v>1600000</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>10400</v>
+        <v>20000</v>
       </c>
       <c r="J19">
-        <v>12700</v>
+        <v>23500</v>
       </c>
       <c r="K19">
-        <v>8650735</v>
+        <v>8751446</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>16000</v>
+        <v>30000</v>
       </c>
       <c r="N19" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="O19" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="P19">
-        <v>2055746777</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>2918221978</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>979078233</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>-3343774083</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>-3525649863</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>-1713494359</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>-4430074915</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>-8304699942</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>-1627684107</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:25">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" t="s">
         <v>48</v>
       </c>
-      <c r="C20" t="s">
-        <v>58</v>
-      </c>
       <c r="D20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E20" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F20">
-        <v>5000000</v>
+        <v>1298000</v>
       </c>
       <c r="G20">
-        <v>5000000</v>
+        <v>1298000</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>2000</v>
+        <v>10400</v>
       </c>
       <c r="J20">
-        <v>2000</v>
+        <v>12700</v>
       </c>
       <c r="K20">
-        <v>5840000</v>
+        <v>8650735</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>2000</v>
+        <v>16000</v>
       </c>
       <c r="N20" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="O20" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2055746777</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2918221978</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>979078233</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>-3343774083</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>-3525649863</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>-1713494359</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>-4430074915</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>-8304699942</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>-1627684107</v>
       </c>
       <c r="Y20" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2348,46 +2366,46 @@
         <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="E21" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F21">
-        <v>1400000</v>
+        <v>5000000</v>
       </c>
       <c r="G21">
-        <v>1400000</v>
+        <v>5000000</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>34000</v>
+        <v>2000</v>
       </c>
       <c r="J21">
-        <v>40000</v>
+        <v>2000</v>
       </c>
       <c r="K21">
-        <v>7942750</v>
+        <v>5840000</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>40000</v>
+        <v>2000</v>
       </c>
       <c r="N21" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="O21" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -2417,84 +2435,161 @@
         <v>0</v>
       </c>
       <c r="Y21" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:25">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22">
+        <v>1400000</v>
+      </c>
+      <c r="G22">
+        <v>1400000</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>34000</v>
+      </c>
+      <c r="J22">
+        <v>40000</v>
+      </c>
+      <c r="K22">
+        <v>7942750</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>40000</v>
+      </c>
+      <c r="N22" t="s">
+        <v>117</v>
+      </c>
+      <c r="O22" t="s">
+        <v>131</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
+      <c r="A23" t="s">
         <v>35</v>
       </c>
-      <c r="C22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" t="s">
-        <v>72</v>
-      </c>
-      <c r="E22" t="s">
-        <v>93</v>
-      </c>
-      <c r="F22">
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23">
         <v>23333334</v>
       </c>
-      <c r="G22">
+      <c r="G23">
         <v>23333334</v>
       </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
         <v>3000</v>
       </c>
-      <c r="J22">
+      <c r="J23">
         <v>3800</v>
       </c>
-      <c r="K22">
+      <c r="K23">
         <v>43477664</v>
       </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>3000</v>
       </c>
-      <c r="N22" t="s">
-        <v>114</v>
-      </c>
-      <c r="O22" t="s">
-        <v>117</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>142</v>
+      <c r="N23" t="s">
+        <v>118</v>
+      </c>
+      <c r="O23" t="s">
+        <v>122</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet1.xlsx
+++ b/datasets/sheet1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="154">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -91,6 +91,9 @@
     <t>주요제품</t>
   </si>
   <si>
+    <t>2024-07-29</t>
+  </si>
+  <si>
     <t>2024-07-23</t>
   </si>
   <si>
@@ -142,7 +145,7 @@
     <t>2024-05-23</t>
   </si>
   <si>
-    <t>2024-07-29</t>
+    <t>2024-07-30</t>
   </si>
   <si>
     <t>2024-07-19</t>
@@ -169,6 +172,9 @@
     <t>2024-05-29</t>
   </si>
   <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
     <t>2024-07-25</t>
   </si>
   <si>
@@ -205,6 +211,9 @@
     <t>2024-07-01</t>
   </si>
   <si>
+    <t>교보</t>
+  </si>
+  <si>
     <t>미래</t>
   </si>
   <si>
@@ -241,6 +250,9 @@
     <t>신한, 한국</t>
   </si>
   <si>
+    <t>교보16호스팩</t>
+  </si>
+  <si>
     <t>뱅크웨어글로벌</t>
   </si>
   <si>
@@ -307,6 +319,9 @@
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
+    <t>1085.71:1</t>
+  </si>
+  <si>
     <t>155.74:1</t>
   </si>
   <si>
@@ -373,6 +388,9 @@
     <t>38.7:1</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>1.52%</t>
   </si>
   <si>
@@ -382,9 +400,6 @@
     <t>5.60%</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>4.50%</t>
   </si>
   <si>
@@ -412,6 +427,9 @@
     <t>0.95%</t>
   </si>
   <si>
+    <t>기업인수합병</t>
+  </si>
+  <si>
     <t>국내외 은행 및 금융기업 대상 코어뱅킹 소프트웨어</t>
   </si>
   <si>
@@ -437,9 +455,6 @@
   </si>
   <si>
     <t>전동기 및 발전기 (범용모터, 서보모터)</t>
-  </si>
-  <si>
-    <t>기업인수합병</t>
   </si>
   <si>
     <t>산업용 및 차량용 라이다(LiDAR)</t>
@@ -818,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y23"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -903,76 +918,76 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F2">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="G2">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="J2">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="K2">
-        <v>10000988</v>
+        <v>6100000</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="O2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="P2">
-        <v>72895458363</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>72913766913</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>11230711680</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>-6524077412</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>-4556157069</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>-3633759729</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>-11528915410</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>-7978634776</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>-3801868433</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -980,76 +995,76 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F3">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="G3">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J3">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K3">
-        <v>14965620</v>
+        <v>10000988</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="P3">
-        <v>1337894447</v>
+        <v>72895458363</v>
       </c>
       <c r="Q3">
-        <v>4495088983</v>
+        <v>72913766913</v>
       </c>
       <c r="R3">
-        <v>99398351</v>
+        <v>11230711680</v>
       </c>
       <c r="S3">
-        <v>-3330678562</v>
+        <v>-6524077412</v>
       </c>
       <c r="T3">
-        <v>-2905069801</v>
+        <v>-4556157069</v>
       </c>
       <c r="U3">
-        <v>-1314068310</v>
+        <v>-3633759729</v>
       </c>
       <c r="V3">
-        <v>-9735376868</v>
+        <v>-11528915410</v>
       </c>
       <c r="W3">
-        <v>-5043515600</v>
+        <v>-7978634776</v>
       </c>
       <c r="X3">
-        <v>-1257080998</v>
+        <v>-3801868433</v>
       </c>
       <c r="Y3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1060,73 +1075,73 @@
         <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F4">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="G4">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>14000</v>
+        <v>7300</v>
       </c>
       <c r="J4">
-        <v>17000</v>
+        <v>8500</v>
       </c>
       <c r="K4">
-        <v>6471740</v>
+        <v>14965620</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="N4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="O4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="P4">
-        <v>5214628820</v>
+        <v>1337894447</v>
       </c>
       <c r="Q4">
-        <v>6009352447</v>
+        <v>4495088983</v>
       </c>
       <c r="R4">
-        <v>965797975</v>
+        <v>99398351</v>
       </c>
       <c r="S4">
-        <v>2015081728</v>
+        <v>-3330678562</v>
       </c>
       <c r="T4">
-        <v>1319755337</v>
+        <v>-2905069801</v>
       </c>
       <c r="U4">
-        <v>-44547594</v>
+        <v>-1314068310</v>
       </c>
       <c r="V4">
-        <v>1503069100</v>
+        <v>-9735376868</v>
       </c>
       <c r="W4">
-        <v>1410469786</v>
+        <v>-5043515600</v>
       </c>
       <c r="X4">
-        <v>24178632</v>
+        <v>-1257080998</v>
       </c>
       <c r="Y4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1137,96 +1152,96 @@
         <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F5">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="G5">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>2000</v>
+        <v>14000</v>
       </c>
       <c r="J5">
-        <v>2000</v>
+        <v>17000</v>
       </c>
       <c r="K5">
-        <v>6345000</v>
+        <v>6471740</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>2000</v>
+        <v>22000</v>
       </c>
       <c r="N5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="O5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>5214628820</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>6009352447</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>965797975</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2015081728</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1319755337</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>-44547594</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1503069100</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1410469786</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>24178632</v>
       </c>
       <c r="Y5" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F6">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="G6">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1238,7 +1253,7 @@
         <v>2000</v>
       </c>
       <c r="K6">
-        <v>4420000</v>
+        <v>6345000</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1247,10 +1262,10 @@
         <v>2000</v>
       </c>
       <c r="N6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="O6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1280,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1291,43 +1306,43 @@
         <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F7">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="G7">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>6200</v>
+        <v>2000</v>
       </c>
       <c r="J7">
-        <v>7700</v>
+        <v>2000</v>
       </c>
       <c r="K7">
-        <v>10830212</v>
+        <v>4420000</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1357,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1365,46 +1380,46 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F8">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="G8">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>2000</v>
+        <v>6200</v>
       </c>
       <c r="J8">
-        <v>2000</v>
+        <v>7700</v>
       </c>
       <c r="K8">
-        <v>5020000</v>
+        <v>10830212</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="N8" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="O8" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1434,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1445,73 +1460,73 @@
         <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F9">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="G9">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="J9">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="K9">
-        <v>7836009</v>
+        <v>5020000</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N9" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="O9" t="s">
         <v>124</v>
       </c>
       <c r="P9">
-        <v>12596039842</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>14910346438</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>16039074617</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>1732604466</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2893667787</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>1613779678</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1558081149</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>2643467726</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>1795726428</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1522,73 +1537,73 @@
         <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F10">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="G10">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>36400</v>
+        <v>9000</v>
       </c>
       <c r="J10">
-        <v>43300</v>
+        <v>12000</v>
       </c>
       <c r="K10">
-        <v>9375694</v>
+        <v>7836009</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="N10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="O10" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="P10">
-        <v>103267682</v>
+        <v>12596039842</v>
       </c>
       <c r="Q10">
-        <v>342201581</v>
+        <v>14910346438</v>
       </c>
       <c r="R10">
-        <v>231425455</v>
+        <v>16039074617</v>
       </c>
       <c r="S10">
-        <v>-7598692896</v>
+        <v>1732604466</v>
       </c>
       <c r="T10">
-        <v>-25822444575</v>
+        <v>2893667787</v>
       </c>
       <c r="U10">
-        <v>-15929213281</v>
+        <v>1613779678</v>
       </c>
       <c r="V10">
-        <v>-6973258680</v>
+        <v>1558081149</v>
       </c>
       <c r="W10">
-        <v>-48433907514</v>
+        <v>2643467726</v>
       </c>
       <c r="X10">
-        <v>-83246975113</v>
+        <v>1795726428</v>
       </c>
       <c r="Y10" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1596,76 +1611,76 @@
         <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F11">
-        <v>3400000</v>
+        <v>1330000</v>
       </c>
       <c r="G11">
-        <v>3400000</v>
+        <v>1330000</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>4500</v>
+        <v>36400</v>
       </c>
       <c r="J11">
-        <v>5500</v>
+        <v>43300</v>
       </c>
       <c r="K11">
-        <v>30888000</v>
+        <v>9375694</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>7000</v>
+        <v>43300</v>
       </c>
       <c r="N11" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="O11" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="P11">
-        <v>85187882584</v>
+        <v>103267682</v>
       </c>
       <c r="Q11">
-        <v>87525689695</v>
+        <v>342201581</v>
       </c>
       <c r="R11">
-        <v>77247394706</v>
+        <v>231425455</v>
       </c>
       <c r="S11">
-        <v>2205797752</v>
+        <v>-7598692896</v>
       </c>
       <c r="T11">
-        <v>4920387020</v>
+        <v>-25822444575</v>
       </c>
       <c r="U11">
-        <v>4336496285</v>
+        <v>-15929213281</v>
       </c>
       <c r="V11">
-        <v>1613954566</v>
+        <v>-6973258680</v>
       </c>
       <c r="W11">
-        <v>3980493669</v>
+        <v>-48433907514</v>
       </c>
       <c r="X11">
-        <v>2646634321</v>
+        <v>-83246975113</v>
       </c>
       <c r="Y11" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1676,73 +1691,73 @@
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F12">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="G12">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>2000</v>
+        <v>4500</v>
       </c>
       <c r="J12">
-        <v>2000</v>
+        <v>5500</v>
       </c>
       <c r="K12">
-        <v>6870000</v>
+        <v>30888000</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="N12" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="O12" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>85187882584</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>87525689695</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>77247394706</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2205797752</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>4920387020</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>4336496285</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1613954566</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>3980493669</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>2646634321</v>
       </c>
       <c r="Y12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1750,46 +1765,46 @@
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F13">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="G13">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>7500</v>
+        <v>2000</v>
       </c>
       <c r="J13">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="K13">
-        <v>17529140</v>
+        <v>6870000</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>11500</v>
+        <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O13" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1819,7 +1834,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1827,46 +1842,46 @@
         <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F14">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="G14">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>2000</v>
+        <v>7500</v>
       </c>
       <c r="J14">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="K14">
-        <v>6930000</v>
+        <v>17529140</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>2000</v>
+        <v>11500</v>
       </c>
       <c r="N14" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O14" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1896,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1904,22 +1919,22 @@
         <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F15">
-        <v>6000000</v>
+        <v>6450000</v>
       </c>
       <c r="G15">
-        <v>6000000</v>
+        <v>6450000</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -1931,7 +1946,7 @@
         <v>2000</v>
       </c>
       <c r="K15">
-        <v>6220000</v>
+        <v>6930000</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1940,10 +1955,10 @@
         <v>2000</v>
       </c>
       <c r="N15" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="O15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -1973,30 +1988,30 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:25">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F16">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="G16">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -2008,7 +2023,7 @@
         <v>2000</v>
       </c>
       <c r="K16">
-        <v>4810000</v>
+        <v>6220000</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2017,10 +2032,10 @@
         <v>2000</v>
       </c>
       <c r="N16" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="O16" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -2050,30 +2065,30 @@
         <v>0</v>
       </c>
       <c r="Y16" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:25">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F17">
-        <v>4750000</v>
+        <v>4000000</v>
       </c>
       <c r="G17">
-        <v>4750000</v>
+        <v>4000000</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -2085,7 +2100,7 @@
         <v>2000</v>
       </c>
       <c r="K17">
-        <v>5480000</v>
+        <v>4810000</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2094,10 +2109,10 @@
         <v>2000</v>
       </c>
       <c r="N17" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="O17" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -2127,84 +2142,84 @@
         <v>0</v>
       </c>
       <c r="Y17" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:25">
       <c r="A18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" t="s">
         <v>38</v>
       </c>
-      <c r="B18" t="s">
-        <v>49</v>
-      </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E18" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F18">
-        <v>1300000</v>
+        <v>4750000</v>
       </c>
       <c r="G18">
-        <v>1300000</v>
+        <v>4750000</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>10500</v>
+        <v>2000</v>
       </c>
       <c r="J18">
-        <v>14000</v>
+        <v>2000</v>
       </c>
       <c r="K18">
-        <v>12293880</v>
+        <v>5480000</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>17000</v>
+        <v>2000</v>
       </c>
       <c r="N18" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="O18" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="P18">
-        <v>1386123525</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>1152944128</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>1885010467</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>-4388824706</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>-7990287699</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>-9803411085</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>-4430563401</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>-7988275689</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>-9916946238</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2212,230 +2227,230 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F19">
-        <v>1600000</v>
+        <v>1300000</v>
       </c>
       <c r="G19">
-        <v>1600000</v>
+        <v>1300000</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>20000</v>
+        <v>10500</v>
       </c>
       <c r="J19">
-        <v>23500</v>
+        <v>14000</v>
       </c>
       <c r="K19">
-        <v>8751446</v>
+        <v>12293880</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>30000</v>
+        <v>17000</v>
       </c>
       <c r="N19" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="O19" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>1386123525</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>1152944128</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1885010467</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>-4388824706</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>-7990287699</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>-9803411085</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>-4430563401</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>-7988275689</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>-9916946238</v>
       </c>
       <c r="Y19" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:25">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F20">
-        <v>1298000</v>
+        <v>1600000</v>
       </c>
       <c r="G20">
-        <v>1298000</v>
+        <v>1600000</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>10400</v>
+        <v>20000</v>
       </c>
       <c r="J20">
-        <v>12700</v>
+        <v>23500</v>
       </c>
       <c r="K20">
-        <v>8650735</v>
+        <v>8751446</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>16000</v>
+        <v>30000</v>
       </c>
       <c r="N20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="O20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="P20">
-        <v>2055746777</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>2918221978</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>979078233</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>-3343774083</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>-3525649863</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>-1713494359</v>
+        <v>0</v>
       </c>
       <c r="V20">
-        <v>-4430074915</v>
+        <v>0</v>
       </c>
       <c r="W20">
-        <v>-8304699942</v>
+        <v>0</v>
       </c>
       <c r="X20">
-        <v>-1627684107</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:25">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
         <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E21" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F21">
-        <v>5000000</v>
+        <v>1298000</v>
       </c>
       <c r="G21">
-        <v>5000000</v>
+        <v>1298000</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>2000</v>
+        <v>10400</v>
       </c>
       <c r="J21">
-        <v>2000</v>
+        <v>12700</v>
       </c>
       <c r="K21">
-        <v>5840000</v>
+        <v>8650735</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>2000</v>
+        <v>16000</v>
       </c>
       <c r="N21" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O21" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2055746777</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2918221978</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>979078233</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>-3343774083</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>-3525649863</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>-1713494359</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>-4430074915</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>-8304699942</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>-1627684107</v>
       </c>
       <c r="Y21" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2443,46 +2458,46 @@
         <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="E22" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F22">
-        <v>1400000</v>
+        <v>5000000</v>
       </c>
       <c r="G22">
-        <v>1400000</v>
+        <v>5000000</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22">
-        <v>34000</v>
+        <v>2000</v>
       </c>
       <c r="J22">
-        <v>40000</v>
+        <v>2000</v>
       </c>
       <c r="K22">
-        <v>7942750</v>
+        <v>5840000</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>40000</v>
+        <v>2000</v>
       </c>
       <c r="N22" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="O22" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -2512,84 +2527,161 @@
         <v>0</v>
       </c>
       <c r="Y22" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:25">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23">
+        <v>1400000</v>
+      </c>
+      <c r="G23">
+        <v>1400000</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>34000</v>
+      </c>
+      <c r="J23">
+        <v>40000</v>
+      </c>
+      <c r="K23">
+        <v>7942750</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>40000</v>
+      </c>
+      <c r="N23" t="s">
+        <v>122</v>
+      </c>
+      <c r="O23" t="s">
+        <v>136</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
+      <c r="A24" t="s">
         <v>36</v>
       </c>
-      <c r="C23" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" t="s">
-        <v>74</v>
-      </c>
-      <c r="E23" t="s">
-        <v>96</v>
-      </c>
-      <c r="F23">
+      <c r="B24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24">
         <v>23333334</v>
       </c>
-      <c r="G23">
+      <c r="G24">
         <v>23333334</v>
       </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
         <v>3000</v>
       </c>
-      <c r="J23">
+      <c r="J24">
         <v>3800</v>
       </c>
-      <c r="K23">
+      <c r="K24">
         <v>43477664</v>
       </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
         <v>3000</v>
       </c>
-      <c r="N23" t="s">
-        <v>118</v>
-      </c>
-      <c r="O23" t="s">
-        <v>122</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>148</v>
+      <c r="N24" t="s">
+        <v>123</v>
+      </c>
+      <c r="O24" t="s">
+        <v>124</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet1.xlsx
+++ b/datasets/sheet1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="148">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -142,9 +142,6 @@
     <t>2024-05-28</t>
   </si>
   <si>
-    <t>2024-05-23</t>
-  </si>
-  <si>
     <t>2024-07-30</t>
   </si>
   <si>
@@ -205,9 +202,6 @@
     <t>2024-06-18</t>
   </si>
   <si>
-    <t>2024-06-14</t>
-  </si>
-  <si>
     <t>2024-07-01</t>
   </si>
   <si>
@@ -313,9 +307,6 @@
     <t>디비금융스팩12호</t>
   </si>
   <si>
-    <t>그리드위즈</t>
-  </si>
-  <si>
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
@@ -382,9 +373,6 @@
     <t>1141.40:1</t>
   </si>
   <si>
-    <t>124.60:1</t>
-  </si>
-  <si>
     <t>38.7:1</t>
   </si>
   <si>
@@ -424,9 +412,6 @@
     <t>9.93%</t>
   </si>
   <si>
-    <t>0.95%</t>
-  </si>
-  <si>
     <t>기업인수합병</t>
   </si>
   <si>
@@ -470,9 +455,6 @@
   </si>
   <si>
     <t>기업인수 및 합병</t>
-  </si>
-  <si>
-    <t>수요관리 서비스, 전기차 충전기 모뎀 등</t>
   </si>
   <si>
     <t>신탁 및 집합투자</t>
@@ -833,7 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -918,16 +900,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F2">
         <v>5800000</v>
@@ -954,10 +936,10 @@
         <v>2000</v>
       </c>
       <c r="N2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -987,7 +969,7 @@
         <v>0</v>
       </c>
       <c r="Y2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -998,13 +980,13 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F3">
         <v>1400000</v>
@@ -1031,10 +1013,10 @@
         <v>16000</v>
       </c>
       <c r="N3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="O3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="P3">
         <v>72895458363</v>
@@ -1064,7 +1046,7 @@
         <v>-3801868433</v>
       </c>
       <c r="Y3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1072,16 +1054,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F4">
         <v>2234000</v>
@@ -1108,10 +1090,10 @@
         <v>10000</v>
       </c>
       <c r="N4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="O4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="P4">
         <v>1337894447</v>
@@ -1141,7 +1123,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1149,16 +1131,16 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F5">
         <v>1350000</v>
@@ -1185,10 +1167,10 @@
         <v>22000</v>
       </c>
       <c r="N5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="P5">
         <v>5214628820</v>
@@ -1218,7 +1200,7 @@
         <v>24178632</v>
       </c>
       <c r="Y5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1226,16 +1208,16 @@
         <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F6">
         <v>6000000</v>
@@ -1262,10 +1244,10 @@
         <v>2000</v>
       </c>
       <c r="N6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="O6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1295,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1303,16 +1285,16 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F7">
         <v>4000000</v>
@@ -1339,10 +1321,10 @@
         <v>2000</v>
       </c>
       <c r="N7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1372,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1380,16 +1362,16 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
         <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F8">
         <v>1618000</v>
@@ -1416,10 +1398,10 @@
         <v>10000</v>
       </c>
       <c r="N8" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="O8" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1449,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1457,16 +1439,16 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F9">
         <v>4000000</v>
@@ -1493,10 +1475,10 @@
         <v>2000</v>
       </c>
       <c r="N9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="O9" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1526,7 +1508,7 @@
         <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1534,16 +1516,16 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F10">
         <v>1810000</v>
@@ -1570,10 +1552,10 @@
         <v>16000</v>
       </c>
       <c r="N10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="O10" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="P10">
         <v>12596039842</v>
@@ -1603,7 +1585,7 @@
         <v>1795726428</v>
       </c>
       <c r="Y10" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1611,16 +1593,16 @@
         <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F11">
         <v>1330000</v>
@@ -1647,10 +1629,10 @@
         <v>43300</v>
       </c>
       <c r="N11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O11" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="P11">
         <v>103267682</v>
@@ -1680,7 +1662,7 @@
         <v>-83246975113</v>
       </c>
       <c r="Y11" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1694,10 +1676,10 @@
         <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F12">
         <v>3400000</v>
@@ -1724,10 +1706,10 @@
         <v>7000</v>
       </c>
       <c r="N12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="O12" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="P12">
         <v>85187882584</v>
@@ -1757,7 +1739,7 @@
         <v>2646634321</v>
       </c>
       <c r="Y12" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1768,13 +1750,13 @@
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F13">
         <v>6250000</v>
@@ -1801,10 +1783,10 @@
         <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O13" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1834,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1845,13 +1827,13 @@
         <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F14">
         <v>2000000</v>
@@ -1878,10 +1860,10 @@
         <v>11500</v>
       </c>
       <c r="N14" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="O14" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1911,7 +1893,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1925,10 +1907,10 @@
         <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F15">
         <v>6450000</v>
@@ -1955,10 +1937,10 @@
         <v>2000</v>
       </c>
       <c r="N15" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="O15" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -1988,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1999,13 +1981,13 @@
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F16">
         <v>6000000</v>
@@ -2032,10 +2014,10 @@
         <v>2000</v>
       </c>
       <c r="N16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="O16" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -2065,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2076,13 +2058,13 @@
         <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F17">
         <v>4000000</v>
@@ -2109,10 +2091,10 @@
         <v>2000</v>
       </c>
       <c r="N17" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O17" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -2142,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="Y17" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2153,13 +2135,13 @@
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E18" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F18">
         <v>4750000</v>
@@ -2186,10 +2168,10 @@
         <v>2000</v>
       </c>
       <c r="N18" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="O18" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -2219,7 +2201,7 @@
         <v>0</v>
       </c>
       <c r="Y18" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2227,16 +2209,16 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F19">
         <v>1300000</v>
@@ -2263,10 +2245,10 @@
         <v>17000</v>
       </c>
       <c r="N19" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="O19" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="P19">
         <v>1386123525</v>
@@ -2296,7 +2278,7 @@
         <v>-9916946238</v>
       </c>
       <c r="Y19" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2310,10 +2292,10 @@
         <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F20">
         <v>1600000</v>
@@ -2340,10 +2322,10 @@
         <v>30000</v>
       </c>
       <c r="N20" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O20" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -2373,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="Y20" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2381,16 +2363,16 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F21">
         <v>1298000</v>
@@ -2417,10 +2399,10 @@
         <v>16000</v>
       </c>
       <c r="N21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O21" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="P21">
         <v>2055746777</v>
@@ -2450,7 +2432,7 @@
         <v>-1627684107</v>
       </c>
       <c r="Y21" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2458,16 +2440,16 @@
         <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F22">
         <v>5000000</v>
@@ -2494,10 +2476,10 @@
         <v>2000</v>
       </c>
       <c r="N22" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="O22" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -2527,54 +2509,54 @@
         <v>0</v>
       </c>
       <c r="Y22" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:25">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="E23" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F23">
-        <v>1400000</v>
+        <v>23333334</v>
       </c>
       <c r="G23">
-        <v>1400000</v>
+        <v>23333334</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23">
-        <v>34000</v>
+        <v>3000</v>
       </c>
       <c r="J23">
-        <v>40000</v>
+        <v>3800</v>
       </c>
       <c r="K23">
-        <v>7942750</v>
+        <v>43477664</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23">
-        <v>40000</v>
+        <v>3000</v>
       </c>
       <c r="N23" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O23" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -2604,84 +2586,7 @@
         <v>0</v>
       </c>
       <c r="Y23" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25">
-      <c r="A24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24" t="s">
-        <v>100</v>
-      </c>
-      <c r="F24">
-        <v>23333334</v>
-      </c>
-      <c r="G24">
-        <v>23333334</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>3000</v>
-      </c>
-      <c r="J24">
-        <v>3800</v>
-      </c>
-      <c r="K24">
-        <v>43477664</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>3000</v>
-      </c>
-      <c r="N24" t="s">
-        <v>123</v>
-      </c>
-      <c r="O24" t="s">
-        <v>124</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
-        <v>0</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>0</v>
-      </c>
-      <c r="V24">
-        <v>0</v>
-      </c>
-      <c r="W24">
-        <v>0</v>
-      </c>
-      <c r="X24">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet1.xlsx
+++ b/datasets/sheet1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="154">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -142,6 +142,9 @@
     <t>2024-05-28</t>
   </si>
   <si>
+    <t>2024-08-02</t>
+  </si>
+  <si>
     <t>2024-07-30</t>
   </si>
   <si>
@@ -169,6 +172,9 @@
     <t>2024-05-29</t>
   </si>
   <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
     <t>2024-08-13</t>
   </si>
   <si>
@@ -205,6 +211,9 @@
     <t>2024-07-01</t>
   </si>
   <si>
+    <t>키움</t>
+  </si>
+  <si>
     <t>교보</t>
   </si>
   <si>
@@ -214,9 +223,6 @@
     <t>삼성</t>
   </si>
   <si>
-    <t>키움</t>
-  </si>
-  <si>
     <t>NH</t>
   </si>
   <si>
@@ -244,6 +250,9 @@
     <t>신한, 한국</t>
   </si>
   <si>
+    <t>유라클</t>
+  </si>
+  <si>
     <t>교보16호스팩</t>
   </si>
   <si>
@@ -310,6 +319,9 @@
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
+    <t>1065.86:1</t>
+  </si>
+  <si>
     <t>1085.71:1</t>
   </si>
   <si>
@@ -376,6 +388,9 @@
     <t>38.7:1</t>
   </si>
   <si>
+    <t>0.55%</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
@@ -410,6 +425,9 @@
   </si>
   <si>
     <t>9.93%</t>
+  </si>
+  <si>
+    <t>모바일 앱 개발 플랫폼</t>
   </si>
   <si>
     <t>기업인수합병</t>
@@ -815,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y23"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -903,43 +921,43 @@
         <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F2">
-        <v>5800000</v>
+        <v>751000</v>
       </c>
       <c r="G2">
-        <v>5800000</v>
+        <v>203700</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>547300</v>
       </c>
       <c r="I2">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="J2">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="K2">
-        <v>6100000</v>
+        <v>4330068</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="N2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="O2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -969,315 +987,315 @@
         <v>0</v>
       </c>
       <c r="Y2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F3">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="G3">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="J3">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="K3">
-        <v>10000988</v>
+        <v>6100000</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="O3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="P3">
-        <v>72895458363</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>72913766913</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>11230711680</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>-6524077412</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>-4556157069</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>-3633759729</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>-11528915410</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>-7978634776</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>-3801868433</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F4">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="G4">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J4">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K4">
-        <v>14965620</v>
+        <v>10000988</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="O4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="P4">
-        <v>1337894447</v>
+        <v>72895458363</v>
       </c>
       <c r="Q4">
-        <v>4495088983</v>
+        <v>72913766913</v>
       </c>
       <c r="R4">
-        <v>99398351</v>
+        <v>11230711680</v>
       </c>
       <c r="S4">
-        <v>-3330678562</v>
+        <v>-6524077412</v>
       </c>
       <c r="T4">
-        <v>-2905069801</v>
+        <v>-4556157069</v>
       </c>
       <c r="U4">
-        <v>-1314068310</v>
+        <v>-3633759729</v>
       </c>
       <c r="V4">
-        <v>-9735376868</v>
+        <v>-11528915410</v>
       </c>
       <c r="W4">
-        <v>-5043515600</v>
+        <v>-7978634776</v>
       </c>
       <c r="X4">
-        <v>-1257080998</v>
+        <v>-3801868433</v>
       </c>
       <c r="Y4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
         <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F5">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="G5">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>14000</v>
+        <v>7300</v>
       </c>
       <c r="J5">
-        <v>17000</v>
+        <v>8500</v>
       </c>
       <c r="K5">
-        <v>6471740</v>
+        <v>14965620</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="N5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="O5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="P5">
-        <v>5214628820</v>
+        <v>1337894447</v>
       </c>
       <c r="Q5">
-        <v>6009352447</v>
+        <v>4495088983</v>
       </c>
       <c r="R5">
-        <v>965797975</v>
+        <v>99398351</v>
       </c>
       <c r="S5">
-        <v>2015081728</v>
+        <v>-3330678562</v>
       </c>
       <c r="T5">
-        <v>1319755337</v>
+        <v>-2905069801</v>
       </c>
       <c r="U5">
-        <v>-44547594</v>
+        <v>-1314068310</v>
       </c>
       <c r="V5">
-        <v>1503069100</v>
+        <v>-9735376868</v>
       </c>
       <c r="W5">
-        <v>1410469786</v>
+        <v>-5043515600</v>
       </c>
       <c r="X5">
-        <v>24178632</v>
+        <v>-1257080998</v>
       </c>
       <c r="Y5" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
         <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F6">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="G6">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>2000</v>
+        <v>14000</v>
       </c>
       <c r="J6">
-        <v>2000</v>
+        <v>17000</v>
       </c>
       <c r="K6">
-        <v>6345000</v>
+        <v>6471740</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>2000</v>
+        <v>22000</v>
       </c>
       <c r="N6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O6" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>5214628820</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>6009352447</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>965797975</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2015081728</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1319755337</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>-44547594</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1503069100</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1410469786</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>24178632</v>
       </c>
       <c r="Y6" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1285,22 +1303,22 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F7">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="G7">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1312,7 +1330,7 @@
         <v>2000</v>
       </c>
       <c r="K7">
-        <v>4420000</v>
+        <v>6345000</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1321,10 +1339,10 @@
         <v>2000</v>
       </c>
       <c r="N7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="O7" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1354,54 +1372,54 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
         <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F8">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="G8">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>6200</v>
+        <v>2000</v>
       </c>
       <c r="J8">
-        <v>7700</v>
+        <v>2000</v>
       </c>
       <c r="K8">
-        <v>10830212</v>
+        <v>4420000</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="O8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1431,54 +1449,54 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F9">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="G9">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>2000</v>
+        <v>6200</v>
       </c>
       <c r="J9">
-        <v>2000</v>
+        <v>7700</v>
       </c>
       <c r="K9">
-        <v>5020000</v>
+        <v>10830212</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="N9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="O9" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1508,362 +1526,362 @@
         <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
         <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F10">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="G10">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="J10">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="K10">
-        <v>7836009</v>
+        <v>5020000</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="O10" t="s">
         <v>125</v>
       </c>
       <c r="P10">
-        <v>12596039842</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>14910346438</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>16039074617</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>1732604466</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>2893667787</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>1613779678</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1558081149</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>2643467726</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>1795726428</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
         <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F11">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="G11">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>36400</v>
+        <v>9000</v>
       </c>
       <c r="J11">
-        <v>43300</v>
+        <v>12000</v>
       </c>
       <c r="K11">
-        <v>9375694</v>
+        <v>7836009</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="N11" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="O11" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="P11">
-        <v>103267682</v>
+        <v>12596039842</v>
       </c>
       <c r="Q11">
-        <v>342201581</v>
+        <v>14910346438</v>
       </c>
       <c r="R11">
-        <v>231425455</v>
+        <v>16039074617</v>
       </c>
       <c r="S11">
-        <v>-7598692896</v>
+        <v>1732604466</v>
       </c>
       <c r="T11">
-        <v>-25822444575</v>
+        <v>2893667787</v>
       </c>
       <c r="U11">
-        <v>-15929213281</v>
+        <v>1613779678</v>
       </c>
       <c r="V11">
-        <v>-6973258680</v>
+        <v>1558081149</v>
       </c>
       <c r="W11">
-        <v>-48433907514</v>
+        <v>2643467726</v>
       </c>
       <c r="X11">
-        <v>-83246975113</v>
+        <v>1795726428</v>
       </c>
       <c r="Y11" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F12">
-        <v>3400000</v>
+        <v>1330000</v>
       </c>
       <c r="G12">
-        <v>3400000</v>
+        <v>1330000</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>4500</v>
+        <v>36400</v>
       </c>
       <c r="J12">
-        <v>5500</v>
+        <v>43300</v>
       </c>
       <c r="K12">
-        <v>30888000</v>
+        <v>9375694</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>7000</v>
+        <v>43300</v>
       </c>
       <c r="N12" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="O12" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="P12">
-        <v>85187882584</v>
+        <v>103267682</v>
       </c>
       <c r="Q12">
-        <v>87525689695</v>
+        <v>342201581</v>
       </c>
       <c r="R12">
-        <v>77247394706</v>
+        <v>231425455</v>
       </c>
       <c r="S12">
-        <v>2205797752</v>
+        <v>-7598692896</v>
       </c>
       <c r="T12">
-        <v>4920387020</v>
+        <v>-25822444575</v>
       </c>
       <c r="U12">
-        <v>4336496285</v>
+        <v>-15929213281</v>
       </c>
       <c r="V12">
-        <v>1613954566</v>
+        <v>-6973258680</v>
       </c>
       <c r="W12">
-        <v>3980493669</v>
+        <v>-48433907514</v>
       </c>
       <c r="X12">
-        <v>2646634321</v>
+        <v>-83246975113</v>
       </c>
       <c r="Y12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:25">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F13">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="G13">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>2000</v>
+        <v>4500</v>
       </c>
       <c r="J13">
-        <v>2000</v>
+        <v>5500</v>
       </c>
       <c r="K13">
-        <v>6870000</v>
+        <v>30888000</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="N13" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="O13" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>85187882584</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>87525689695</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>77247394706</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>2205797752</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>4920387020</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>4336496285</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1613954566</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>3980493669</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>2646634321</v>
       </c>
       <c r="Y13" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:25">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F14">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="G14">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>7500</v>
+        <v>2000</v>
       </c>
       <c r="J14">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="K14">
-        <v>17529140</v>
+        <v>6870000</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>11500</v>
+        <v>2000</v>
       </c>
       <c r="N14" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1893,54 +1911,54 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F15">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="G15">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>2000</v>
+        <v>7500</v>
       </c>
       <c r="J15">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="K15">
-        <v>6930000</v>
+        <v>17529140</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15">
-        <v>2000</v>
+        <v>11500</v>
       </c>
       <c r="N15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="O15" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -1970,30 +1988,30 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:25">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F16">
-        <v>6000000</v>
+        <v>6450000</v>
       </c>
       <c r="G16">
-        <v>6000000</v>
+        <v>6450000</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -2005,7 +2023,7 @@
         <v>2000</v>
       </c>
       <c r="K16">
-        <v>6220000</v>
+        <v>6930000</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2014,10 +2032,10 @@
         <v>2000</v>
       </c>
       <c r="N16" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="O16" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -2047,30 +2065,30 @@
         <v>0</v>
       </c>
       <c r="Y16" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F17">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="G17">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -2082,7 +2100,7 @@
         <v>2000</v>
       </c>
       <c r="K17">
-        <v>4810000</v>
+        <v>6220000</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2091,10 +2109,10 @@
         <v>2000</v>
       </c>
       <c r="N17" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="O17" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -2124,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="Y17" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2135,19 +2153,19 @@
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F18">
-        <v>4750000</v>
+        <v>4000000</v>
       </c>
       <c r="G18">
-        <v>4750000</v>
+        <v>4000000</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -2159,7 +2177,7 @@
         <v>2000</v>
       </c>
       <c r="K18">
-        <v>5480000</v>
+        <v>4810000</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -2168,10 +2186,10 @@
         <v>2000</v>
       </c>
       <c r="N18" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="O18" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -2201,392 +2219,469 @@
         <v>0</v>
       </c>
       <c r="Y18" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:25">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F19">
-        <v>1300000</v>
+        <v>4750000</v>
       </c>
       <c r="G19">
-        <v>1300000</v>
+        <v>4750000</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>10500</v>
+        <v>2000</v>
       </c>
       <c r="J19">
-        <v>14000</v>
+        <v>2000</v>
       </c>
       <c r="K19">
-        <v>12293880</v>
+        <v>5480000</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>17000</v>
+        <v>2000</v>
       </c>
       <c r="N19" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="O19" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="P19">
-        <v>1386123525</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>1152944128</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>1885010467</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>-4388824706</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>-7990287699</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>-9803411085</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>-4430563401</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>-7988275689</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>-9916946238</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:25">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D20" t="s">
         <v>73</v>
       </c>
       <c r="E20" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F20">
-        <v>1600000</v>
+        <v>1300000</v>
       </c>
       <c r="G20">
-        <v>1600000</v>
+        <v>1300000</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>20000</v>
+        <v>10500</v>
       </c>
       <c r="J20">
-        <v>23500</v>
+        <v>14000</v>
       </c>
       <c r="K20">
-        <v>8751446</v>
+        <v>12293880</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>30000</v>
+        <v>17000</v>
       </c>
       <c r="N20" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="O20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>1386123525</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>1152944128</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1885010467</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>-4388824706</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>-7990287699</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>-9803411085</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>-4430563401</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>-7988275689</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>-9916946238</v>
       </c>
       <c r="Y20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:25">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F21">
-        <v>1298000</v>
+        <v>1600000</v>
       </c>
       <c r="G21">
-        <v>1298000</v>
+        <v>1600000</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>10400</v>
+        <v>20000</v>
       </c>
       <c r="J21">
-        <v>12700</v>
+        <v>23500</v>
       </c>
       <c r="K21">
-        <v>8650735</v>
+        <v>8751446</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>16000</v>
+        <v>30000</v>
       </c>
       <c r="N21" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="O21" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="P21">
-        <v>2055746777</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>2918221978</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>979078233</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>-3343774083</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>-3525649863</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>-1713494359</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>-4430074915</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>-8304699942</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>-1627684107</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:25">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E22" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F22">
-        <v>5000000</v>
+        <v>1298000</v>
       </c>
       <c r="G22">
-        <v>5000000</v>
+        <v>1298000</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22">
-        <v>2000</v>
+        <v>10400</v>
       </c>
       <c r="J22">
-        <v>2000</v>
+        <v>12700</v>
       </c>
       <c r="K22">
-        <v>5840000</v>
+        <v>8650735</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>2000</v>
+        <v>16000</v>
       </c>
       <c r="N22" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="O22" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2055746777</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2918221978</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>979078233</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>-3343774083</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>-3525649863</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>-1713494359</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>-4430074915</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>-8304699942</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>-1627684107</v>
       </c>
       <c r="Y22" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:25">
       <c r="A23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23">
+        <v>5000000</v>
+      </c>
+      <c r="G23">
+        <v>5000000</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>2000</v>
+      </c>
+      <c r="J23">
+        <v>2000</v>
+      </c>
+      <c r="K23">
+        <v>5840000</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>2000</v>
+      </c>
+      <c r="N23" t="s">
+        <v>122</v>
+      </c>
+      <c r="O23" t="s">
+        <v>125</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
+      <c r="A24" t="s">
         <v>36</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B24" t="s">
         <v>37</v>
       </c>
-      <c r="C23" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" t="s">
-        <v>75</v>
-      </c>
-      <c r="E23" t="s">
-        <v>97</v>
-      </c>
-      <c r="F23">
+      <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24">
         <v>23333334</v>
       </c>
-      <c r="G23">
+      <c r="G24">
         <v>23333334</v>
       </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
         <v>3000</v>
       </c>
-      <c r="J23">
+      <c r="J24">
         <v>3800</v>
       </c>
-      <c r="K23">
+      <c r="K24">
         <v>43477664</v>
       </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
         <v>3000</v>
       </c>
-      <c r="N23" t="s">
-        <v>119</v>
-      </c>
-      <c r="O23" t="s">
-        <v>120</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>147</v>
+      <c r="N24" t="s">
+        <v>123</v>
+      </c>
+      <c r="O24" t="s">
+        <v>125</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet1.xlsx
+++ b/datasets/sheet1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="149">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -94,6 +94,9 @@
     <t>2024-07-31</t>
   </si>
   <si>
+    <t>2024-08-05</t>
+  </si>
+  <si>
     <t>2024-07-30</t>
   </si>
   <si>
@@ -142,9 +145,6 @@
     <t>2024-08-06</t>
   </si>
   <si>
-    <t>2024-08-05</t>
-  </si>
-  <si>
     <t>2024-08-02</t>
   </si>
   <si>
@@ -169,6 +169,9 @@
     <t>2024-08-21</t>
   </si>
   <si>
+    <t>2024-08-22</t>
+  </si>
+  <si>
     <t>2024-08-20</t>
   </si>
   <si>
@@ -205,6 +208,9 @@
     <t>한국</t>
   </si>
   <si>
+    <t>대신</t>
+  </si>
+  <si>
     <t>하나</t>
   </si>
   <si>
@@ -226,9 +232,6 @@
     <t>SK</t>
   </si>
   <si>
-    <t>대신</t>
-  </si>
-  <si>
     <t>엘에스</t>
   </si>
   <si>
@@ -241,6 +244,9 @@
     <t>티디에스팜</t>
   </si>
   <si>
+    <t>대신밸런스제18호스팩</t>
+  </si>
+  <si>
     <t>케이쓰리아이</t>
   </si>
   <si>
@@ -301,6 +307,9 @@
     <t>1331.20:1</t>
   </si>
   <si>
+    <t>1069.96:1</t>
+  </si>
+  <si>
     <t>239.23:1</t>
   </si>
   <si>
@@ -361,6 +370,9 @@
     <t>4.23%</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>1.03%</t>
   </si>
   <si>
@@ -370,9 +382,6 @@
     <t>0.55%</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>1.52%</t>
   </si>
   <si>
@@ -401,6 +410,9 @@
   </si>
   <si>
     <t>경피약물전달시스템(습포제, 첩부제)</t>
+  </si>
+  <si>
+    <t>금융 지원 서비스업</t>
   </si>
   <si>
     <t>XR 실감형콘텐츠</t>
@@ -806,7 +818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -891,16 +903,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F2">
         <v>1000000</v>
@@ -927,10 +939,10 @@
         <v>13000</v>
       </c>
       <c r="N2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="O2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="P2">
         <v>25588</v>
@@ -960,7 +972,7 @@
         <v>809</v>
       </c>
       <c r="Y2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -974,70 +986,70 @@
         <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F3">
-        <v>1400000</v>
+        <v>6500000</v>
       </c>
       <c r="G3">
-        <v>1400000</v>
+        <v>6500000</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>12500</v>
+        <v>2000</v>
       </c>
       <c r="J3">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="K3">
-        <v>7486442</v>
+        <v>7910000</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="N3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="O3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P3">
-        <v>10740898602</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>13058877126</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>3506428302</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>1748628548</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>1115790858</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>191527654</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>1491084554</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>1185231988</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>219774608</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1045,123 +1057,123 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F4">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="G4">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>24000</v>
+        <v>12500</v>
       </c>
       <c r="J4">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="K4">
-        <v>8008066</v>
+        <v>7486442</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="N4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>10740898602</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>13058877126</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>3506428302</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1748628548</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>1115790858</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>191527654</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1491084554</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1185231988</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>219774608</v>
       </c>
       <c r="Y4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
         <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F5">
-        <v>751000</v>
+        <v>1000000</v>
       </c>
       <c r="G5">
-        <v>203700</v>
+        <v>1000000</v>
       </c>
       <c r="H5">
-        <v>547300</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="J5">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="K5">
-        <v>4330068</v>
+        <v>8008066</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="N5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="O5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1191,54 +1203,54 @@
         <v>0</v>
       </c>
       <c r="Y5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
         <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F6">
-        <v>5800000</v>
+        <v>751000</v>
       </c>
       <c r="G6">
-        <v>5800000</v>
+        <v>203700</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>547300</v>
       </c>
       <c r="I6">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="J6">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="K6">
-        <v>6100000</v>
+        <v>4330068</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="N6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1268,7 +1280,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1282,70 +1294,70 @@
         <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F7">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="G7">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="J7">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="K7">
-        <v>10000988</v>
+        <v>6100000</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="O7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P7">
-        <v>72895458363</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>72913766913</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>11230711680</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>-6524077412</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>-4556157069</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>-3633759729</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>-11528915410</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>-7978634776</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>-3801868433</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1353,76 +1365,76 @@
         <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F8">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="G8">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J8">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K8">
-        <v>14965620</v>
+        <v>10000988</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="P8">
-        <v>1337894447</v>
+        <v>72895458363</v>
       </c>
       <c r="Q8">
-        <v>4495088983</v>
+        <v>72913766913</v>
       </c>
       <c r="R8">
-        <v>99398351</v>
+        <v>11230711680</v>
       </c>
       <c r="S8">
-        <v>-3330678562</v>
+        <v>-6524077412</v>
       </c>
       <c r="T8">
-        <v>-2905069801</v>
+        <v>-4556157069</v>
       </c>
       <c r="U8">
-        <v>-1314068310</v>
+        <v>-3633759729</v>
       </c>
       <c r="V8">
-        <v>-9735376868</v>
+        <v>-11528915410</v>
       </c>
       <c r="W8">
-        <v>-5043515600</v>
+        <v>-7978634776</v>
       </c>
       <c r="X8">
-        <v>-1257080998</v>
+        <v>-3801868433</v>
       </c>
       <c r="Y8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1430,76 +1442,76 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F9">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="G9">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>14000</v>
+        <v>7300</v>
       </c>
       <c r="J9">
-        <v>17000</v>
+        <v>8500</v>
       </c>
       <c r="K9">
-        <v>6471740</v>
+        <v>14965620</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="N9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="P9">
-        <v>5214628820</v>
+        <v>1337894447</v>
       </c>
       <c r="Q9">
-        <v>6009352447</v>
+        <v>4495088983</v>
       </c>
       <c r="R9">
-        <v>965797975</v>
+        <v>99398351</v>
       </c>
       <c r="S9">
-        <v>2015081728</v>
+        <v>-3330678562</v>
       </c>
       <c r="T9">
-        <v>1319755337</v>
+        <v>-2905069801</v>
       </c>
       <c r="U9">
-        <v>-44547594</v>
+        <v>-1314068310</v>
       </c>
       <c r="V9">
-        <v>1503069100</v>
+        <v>-9735376868</v>
       </c>
       <c r="W9">
-        <v>1410469786</v>
+        <v>-5043515600</v>
       </c>
       <c r="X9">
-        <v>24178632</v>
+        <v>-1257080998</v>
       </c>
       <c r="Y9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1507,99 +1519,99 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F10">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="G10">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>2000</v>
+        <v>14000</v>
       </c>
       <c r="J10">
-        <v>2000</v>
+        <v>17000</v>
       </c>
       <c r="K10">
-        <v>6345000</v>
+        <v>6471740</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>2000</v>
+        <v>22000</v>
       </c>
       <c r="N10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="O10" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>5214628820</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>6009352447</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>965797975</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2015081728</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1319755337</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>-44547594</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1503069100</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1410469786</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>24178632</v>
       </c>
       <c r="Y10" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:25">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
         <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F11">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="G11">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1611,7 +1623,7 @@
         <v>2000</v>
       </c>
       <c r="K11">
-        <v>4420000</v>
+        <v>6345000</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1620,7 +1632,7 @@
         <v>2000</v>
       </c>
       <c r="N11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="O11" t="s">
         <v>118</v>
@@ -1653,7 +1665,7 @@
         <v>0</v>
       </c>
       <c r="Y11" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1661,46 +1673,46 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F12">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="G12">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>6200</v>
+        <v>2000</v>
       </c>
       <c r="J12">
-        <v>7700</v>
+        <v>2000</v>
       </c>
       <c r="K12">
-        <v>10830212</v>
+        <v>4420000</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="O12" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1730,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1741,43 +1753,43 @@
         <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F13">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="G13">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>2000</v>
+        <v>6200</v>
       </c>
       <c r="J13">
-        <v>2000</v>
+        <v>7700</v>
       </c>
       <c r="K13">
-        <v>5020000</v>
+        <v>10830212</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="N13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O13" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1807,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1815,76 +1827,76 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
         <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F14">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="G14">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="J14">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="K14">
-        <v>7836009</v>
+        <v>5020000</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O14" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="P14">
-        <v>12596039842</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>14910346438</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>16039074617</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>1732604466</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>2893667787</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>1613779678</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1558081149</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>2643467726</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>1795726428</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1892,76 +1904,76 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
         <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F15">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="G15">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>36400</v>
+        <v>9000</v>
       </c>
       <c r="J15">
-        <v>43300</v>
+        <v>12000</v>
       </c>
       <c r="K15">
-        <v>9375694</v>
+        <v>7836009</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="N15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="O15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="P15">
-        <v>103267682</v>
+        <v>12596039842</v>
       </c>
       <c r="Q15">
-        <v>342201581</v>
+        <v>14910346438</v>
       </c>
       <c r="R15">
-        <v>231425455</v>
+        <v>16039074617</v>
       </c>
       <c r="S15">
-        <v>-7598692896</v>
+        <v>1732604466</v>
       </c>
       <c r="T15">
-        <v>-25822444575</v>
+        <v>2893667787</v>
       </c>
       <c r="U15">
-        <v>-15929213281</v>
+        <v>1613779678</v>
       </c>
       <c r="V15">
-        <v>-6973258680</v>
+        <v>1558081149</v>
       </c>
       <c r="W15">
-        <v>-48433907514</v>
+        <v>2643467726</v>
       </c>
       <c r="X15">
-        <v>-83246975113</v>
+        <v>1795726428</v>
       </c>
       <c r="Y15" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1969,76 +1981,76 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F16">
-        <v>3400000</v>
+        <v>1330000</v>
       </c>
       <c r="G16">
-        <v>3400000</v>
+        <v>1330000</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>4500</v>
+        <v>36400</v>
       </c>
       <c r="J16">
-        <v>5500</v>
+        <v>43300</v>
       </c>
       <c r="K16">
-        <v>30888000</v>
+        <v>9375694</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>7000</v>
+        <v>43300</v>
       </c>
       <c r="N16" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O16" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P16">
-        <v>85187882584</v>
+        <v>103267682</v>
       </c>
       <c r="Q16">
-        <v>87525689695</v>
+        <v>342201581</v>
       </c>
       <c r="R16">
-        <v>77247394706</v>
+        <v>231425455</v>
       </c>
       <c r="S16">
-        <v>2205797752</v>
+        <v>-7598692896</v>
       </c>
       <c r="T16">
-        <v>4920387020</v>
+        <v>-25822444575</v>
       </c>
       <c r="U16">
-        <v>4336496285</v>
+        <v>-15929213281</v>
       </c>
       <c r="V16">
-        <v>1613954566</v>
+        <v>-6973258680</v>
       </c>
       <c r="W16">
-        <v>3980493669</v>
+        <v>-48433907514</v>
       </c>
       <c r="X16">
-        <v>2646634321</v>
+        <v>-83246975113</v>
       </c>
       <c r="Y16" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2049,73 +2061,73 @@
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F17">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="G17">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>2000</v>
+        <v>4500</v>
       </c>
       <c r="J17">
-        <v>2000</v>
+        <v>5500</v>
       </c>
       <c r="K17">
-        <v>6870000</v>
+        <v>30888000</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="N17" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O17" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>85187882584</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>87525689695</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>77247394706</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>2205797752</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>4920387020</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>4336496285</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1613954566</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>3980493669</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>2646634321</v>
       </c>
       <c r="Y17" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2123,46 +2135,46 @@
         <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
         <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F18">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="G18">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>7500</v>
+        <v>2000</v>
       </c>
       <c r="J18">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="K18">
-        <v>17529140</v>
+        <v>6870000</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>11500</v>
+        <v>2000</v>
       </c>
       <c r="N18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="O18" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -2192,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="Y18" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2200,46 +2212,46 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F19">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="G19">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>2000</v>
+        <v>7500</v>
       </c>
       <c r="J19">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="K19">
-        <v>6930000</v>
+        <v>17529140</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>2000</v>
+        <v>11500</v>
       </c>
       <c r="N19" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O19" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -2269,7 +2281,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2277,46 +2289,46 @@
         <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F20">
-        <v>1600000</v>
+        <v>6450000</v>
       </c>
       <c r="G20">
-        <v>1600000</v>
+        <v>6450000</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="J20">
-        <v>23500</v>
+        <v>2000</v>
       </c>
       <c r="K20">
-        <v>8751446</v>
+        <v>6930000</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="N20" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="O20" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -2346,84 +2358,161 @@
         <v>0</v>
       </c>
       <c r="Y20" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:25">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="D21" t="s">
         <v>73</v>
       </c>
       <c r="E21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F21">
+        <v>1600000</v>
+      </c>
+      <c r="G21">
+        <v>1600000</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>20000</v>
+      </c>
+      <c r="J21">
+        <v>23500</v>
+      </c>
+      <c r="K21">
+        <v>8751446</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>30000</v>
+      </c>
+      <c r="N21" t="s">
+        <v>115</v>
+      </c>
+      <c r="O21" t="s">
+        <v>130</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22">
         <v>23333334</v>
       </c>
-      <c r="G21">
+      <c r="G22">
         <v>23333334</v>
       </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
         <v>3000</v>
       </c>
-      <c r="J21">
+      <c r="J22">
         <v>3800</v>
       </c>
-      <c r="K21">
+      <c r="K22">
         <v>43477664</v>
       </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
         <v>3000</v>
       </c>
-      <c r="N21" t="s">
-        <v>113</v>
-      </c>
-      <c r="O21" t="s">
+      <c r="N22" t="s">
+        <v>116</v>
+      </c>
+      <c r="O22" t="s">
         <v>118</v>
       </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>144</v>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet1.xlsx
+++ b/datasets/sheet1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="155">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -91,6 +91,9 @@
     <t>주요제품</t>
   </si>
   <si>
+    <t>2024-08-02</t>
+  </si>
+  <si>
     <t>2024-07-31</t>
   </si>
   <si>
@@ -142,12 +145,12 @@
     <t>2024-05-30</t>
   </si>
   <si>
+    <t>2024-08-08</t>
+  </si>
+  <si>
     <t>2024-08-06</t>
   </si>
   <si>
-    <t>2024-08-02</t>
-  </si>
-  <si>
     <t>2024-07-19</t>
   </si>
   <si>
@@ -166,6 +169,9 @@
     <t>2024-06-17</t>
   </si>
   <si>
+    <t>2024-08-23</t>
+  </si>
+  <si>
     <t>2024-08-21</t>
   </si>
   <si>
@@ -205,6 +211,9 @@
     <t>2024-07-01</t>
   </si>
   <si>
+    <t>NH</t>
+  </si>
+  <si>
     <t>한국</t>
   </si>
   <si>
@@ -226,9 +235,6 @@
     <t>삼성</t>
   </si>
   <si>
-    <t>NH</t>
-  </si>
-  <si>
     <t>SK</t>
   </si>
   <si>
@@ -241,6 +247,9 @@
     <t>신한, 한국</t>
   </si>
   <si>
+    <t>이엔셀</t>
+  </si>
+  <si>
     <t>티디에스팜</t>
   </si>
   <si>
@@ -304,6 +313,9 @@
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
+    <t>949.3:1</t>
+  </si>
+  <si>
     <t>1331.20:1</t>
   </si>
   <si>
@@ -367,6 +379,9 @@
     <t>38.7:1</t>
   </si>
   <si>
+    <t>0.24%</t>
+  </si>
+  <si>
     <t>4.23%</t>
   </si>
   <si>
@@ -407,6 +422,9 @@
   </si>
   <si>
     <t>12.44%</t>
+  </si>
+  <si>
+    <t>첨단바이오의약품 위탁개발생산(CDMO) 서비스 / 차세대 세포,유전자 치료제</t>
   </si>
   <si>
     <t>경피약물전달시스템(습포제, 첩부제)</t>
@@ -818,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y22"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -903,76 +921,76 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F2">
-        <v>1000000</v>
+        <v>1566800</v>
       </c>
       <c r="G2">
-        <v>500000</v>
+        <v>1566800</v>
       </c>
       <c r="H2">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>9500</v>
+        <v>13600</v>
       </c>
       <c r="J2">
-        <v>10700</v>
+        <v>15300</v>
       </c>
       <c r="K2">
-        <v>5530000</v>
+        <v>9349954</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>13000</v>
+        <v>15300</v>
       </c>
       <c r="N2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="P2">
-        <v>25588</v>
+        <v>7367362</v>
       </c>
       <c r="Q2">
-        <v>30049</v>
+        <v>10525887</v>
       </c>
       <c r="R2">
-        <v>7363</v>
+        <v>1790340</v>
       </c>
       <c r="S2">
-        <v>3780</v>
+        <v>-9315442</v>
       </c>
       <c r="T2">
-        <v>5016</v>
+        <v>-11755057</v>
       </c>
       <c r="U2">
-        <v>938</v>
+        <v>-2929307</v>
       </c>
       <c r="V2">
-        <v>3456</v>
+        <v>-45566953</v>
       </c>
       <c r="W2">
-        <v>4688</v>
+        <v>-5053520</v>
       </c>
       <c r="X2">
-        <v>809</v>
+        <v>-2903334</v>
       </c>
       <c r="Y2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -980,76 +998,76 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F3">
-        <v>6500000</v>
+        <v>1000000</v>
       </c>
       <c r="G3">
-        <v>6500000</v>
+        <v>500000</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="I3">
-        <v>2000</v>
+        <v>9500</v>
       </c>
       <c r="J3">
-        <v>2000</v>
+        <v>10700</v>
       </c>
       <c r="K3">
-        <v>7910000</v>
+        <v>5530000</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="N3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="O3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>25588</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>30049</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>7363</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>3780</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>5016</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>938</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>3456</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>4688</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>809</v>
       </c>
       <c r="Y3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1057,76 +1075,76 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F4">
-        <v>1400000</v>
+        <v>6500000</v>
       </c>
       <c r="G4">
-        <v>1400000</v>
+        <v>6500000</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>12500</v>
+        <v>2000</v>
       </c>
       <c r="J4">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="K4">
-        <v>7486442</v>
+        <v>7910000</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="N4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="O4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="P4">
-        <v>10740898602</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>13058877126</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>3506428302</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>1748628548</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>1115790858</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>191527654</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1491084554</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1185231988</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>219774608</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1134,123 +1152,123 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F5">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="G5">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>24000</v>
+        <v>12500</v>
       </c>
       <c r="J5">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="K5">
-        <v>8008066</v>
+        <v>7486442</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="N5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="O5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>10740898602</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>13058877126</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>3506428302</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1748628548</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1115790858</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>191527654</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1491084554</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1185231988</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>219774608</v>
       </c>
       <c r="Y5" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
         <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F6">
-        <v>751000</v>
+        <v>1000000</v>
       </c>
       <c r="G6">
-        <v>203700</v>
+        <v>1000000</v>
       </c>
       <c r="H6">
-        <v>547300</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="J6">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="K6">
-        <v>4330068</v>
+        <v>8008066</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="N6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="O6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1280,54 +1298,54 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:25">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F7">
-        <v>5800000</v>
+        <v>751000</v>
       </c>
       <c r="G7">
-        <v>5800000</v>
+        <v>203700</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>547300</v>
       </c>
       <c r="I7">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="J7">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="K7">
-        <v>6100000</v>
+        <v>4330068</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="N7" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="O7" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1357,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1368,73 +1386,73 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F8">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="G8">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="J8">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="K8">
-        <v>10000988</v>
+        <v>6100000</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P8">
-        <v>72895458363</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>72913766913</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>11230711680</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>-6524077412</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>-4556157069</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>-3633759729</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>-11528915410</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>-7978634776</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>-3801868433</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1442,76 +1460,76 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F9">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="G9">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J9">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K9">
-        <v>14965620</v>
+        <v>10000988</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="O9" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="P9">
-        <v>1337894447</v>
+        <v>72895458363</v>
       </c>
       <c r="Q9">
-        <v>4495088983</v>
+        <v>72913766913</v>
       </c>
       <c r="R9">
-        <v>99398351</v>
+        <v>11230711680</v>
       </c>
       <c r="S9">
-        <v>-3330678562</v>
+        <v>-6524077412</v>
       </c>
       <c r="T9">
-        <v>-2905069801</v>
+        <v>-4556157069</v>
       </c>
       <c r="U9">
-        <v>-1314068310</v>
+        <v>-3633759729</v>
       </c>
       <c r="V9">
-        <v>-9735376868</v>
+        <v>-11528915410</v>
       </c>
       <c r="W9">
-        <v>-5043515600</v>
+        <v>-7978634776</v>
       </c>
       <c r="X9">
-        <v>-1257080998</v>
+        <v>-3801868433</v>
       </c>
       <c r="Y9" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1522,73 +1540,73 @@
         <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F10">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="G10">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>14000</v>
+        <v>7300</v>
       </c>
       <c r="J10">
-        <v>17000</v>
+        <v>8500</v>
       </c>
       <c r="K10">
-        <v>6471740</v>
+        <v>14965620</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="O10" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="P10">
-        <v>5214628820</v>
+        <v>1337894447</v>
       </c>
       <c r="Q10">
-        <v>6009352447</v>
+        <v>4495088983</v>
       </c>
       <c r="R10">
-        <v>965797975</v>
+        <v>99398351</v>
       </c>
       <c r="S10">
-        <v>2015081728</v>
+        <v>-3330678562</v>
       </c>
       <c r="T10">
-        <v>1319755337</v>
+        <v>-2905069801</v>
       </c>
       <c r="U10">
-        <v>-44547594</v>
+        <v>-1314068310</v>
       </c>
       <c r="V10">
-        <v>1503069100</v>
+        <v>-9735376868</v>
       </c>
       <c r="W10">
-        <v>1410469786</v>
+        <v>-5043515600</v>
       </c>
       <c r="X10">
-        <v>24178632</v>
+        <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1599,96 +1617,96 @@
         <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F11">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="G11">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>2000</v>
+        <v>14000</v>
       </c>
       <c r="J11">
-        <v>2000</v>
+        <v>17000</v>
       </c>
       <c r="K11">
-        <v>6345000</v>
+        <v>6471740</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>2000</v>
+        <v>22000</v>
       </c>
       <c r="N11" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="O11" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>5214628820</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>6009352447</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>965797975</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2015081728</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1319755337</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>-44547594</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1503069100</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1410469786</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>24178632</v>
       </c>
       <c r="Y11" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:25">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F12">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="G12">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1700,7 +1718,7 @@
         <v>2000</v>
       </c>
       <c r="K12">
-        <v>4420000</v>
+        <v>6345000</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1709,10 +1727,10 @@
         <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="O12" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1742,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1753,43 +1771,43 @@
         <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F13">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="G13">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>6200</v>
+        <v>2000</v>
       </c>
       <c r="J13">
-        <v>7700</v>
+        <v>2000</v>
       </c>
       <c r="K13">
-        <v>10830212</v>
+        <v>4420000</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="O13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1819,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1827,46 +1845,46 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F14">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="G14">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>2000</v>
+        <v>6200</v>
       </c>
       <c r="J14">
-        <v>2000</v>
+        <v>7700</v>
       </c>
       <c r="K14">
-        <v>5020000</v>
+        <v>10830212</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="N14" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="O14" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1896,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1907,73 +1925,73 @@
         <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F15">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="G15">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="J15">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="K15">
-        <v>7836009</v>
+        <v>5020000</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N15" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="O15" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="P15">
-        <v>12596039842</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>14910346438</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>16039074617</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>1732604466</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>2893667787</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>1613779678</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>1558081149</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>2643467726</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>1795726428</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1984,73 +2002,73 @@
         <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F16">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="G16">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>36400</v>
+        <v>9000</v>
       </c>
       <c r="J16">
-        <v>43300</v>
+        <v>12000</v>
       </c>
       <c r="K16">
-        <v>9375694</v>
+        <v>7836009</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="N16" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O16" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="P16">
-        <v>103267682</v>
+        <v>12596039842</v>
       </c>
       <c r="Q16">
-        <v>342201581</v>
+        <v>14910346438</v>
       </c>
       <c r="R16">
-        <v>231425455</v>
+        <v>16039074617</v>
       </c>
       <c r="S16">
-        <v>-7598692896</v>
+        <v>1732604466</v>
       </c>
       <c r="T16">
-        <v>-25822444575</v>
+        <v>2893667787</v>
       </c>
       <c r="U16">
-        <v>-15929213281</v>
+        <v>1613779678</v>
       </c>
       <c r="V16">
-        <v>-6973258680</v>
+        <v>1558081149</v>
       </c>
       <c r="W16">
-        <v>-48433907514</v>
+        <v>2643467726</v>
       </c>
       <c r="X16">
-        <v>-83246975113</v>
+        <v>1795726428</v>
       </c>
       <c r="Y16" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2058,76 +2076,76 @@
         <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F17">
-        <v>3400000</v>
+        <v>1330000</v>
       </c>
       <c r="G17">
-        <v>3400000</v>
+        <v>1330000</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>4500</v>
+        <v>36400</v>
       </c>
       <c r="J17">
-        <v>5500</v>
+        <v>43300</v>
       </c>
       <c r="K17">
-        <v>30888000</v>
+        <v>9375694</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>7000</v>
+        <v>43300</v>
       </c>
       <c r="N17" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="O17" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="P17">
-        <v>85187882584</v>
+        <v>103267682</v>
       </c>
       <c r="Q17">
-        <v>87525689695</v>
+        <v>342201581</v>
       </c>
       <c r="R17">
-        <v>77247394706</v>
+        <v>231425455</v>
       </c>
       <c r="S17">
-        <v>2205797752</v>
+        <v>-7598692896</v>
       </c>
       <c r="T17">
-        <v>4920387020</v>
+        <v>-25822444575</v>
       </c>
       <c r="U17">
-        <v>4336496285</v>
+        <v>-15929213281</v>
       </c>
       <c r="V17">
-        <v>1613954566</v>
+        <v>-6973258680</v>
       </c>
       <c r="W17">
-        <v>3980493669</v>
+        <v>-48433907514</v>
       </c>
       <c r="X17">
-        <v>2646634321</v>
+        <v>-83246975113</v>
       </c>
       <c r="Y17" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2138,73 +2156,73 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E18" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F18">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="G18">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>2000</v>
+        <v>4500</v>
       </c>
       <c r="J18">
-        <v>2000</v>
+        <v>5500</v>
       </c>
       <c r="K18">
-        <v>6870000</v>
+        <v>30888000</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="N18" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="O18" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>85187882584</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>87525689695</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>77247394706</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>2205797752</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>4920387020</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>4336496285</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1613954566</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>3980493669</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>2646634321</v>
       </c>
       <c r="Y18" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2212,46 +2230,46 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E19" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F19">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="G19">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>7500</v>
+        <v>2000</v>
       </c>
       <c r="J19">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="K19">
-        <v>17529140</v>
+        <v>6870000</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>11500</v>
+        <v>2000</v>
       </c>
       <c r="N19" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="O19" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -2281,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2289,46 +2307,46 @@
         <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E20" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F20">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="G20">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>2000</v>
+        <v>7500</v>
       </c>
       <c r="J20">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="K20">
-        <v>6930000</v>
+        <v>17529140</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>2000</v>
+        <v>11500</v>
       </c>
       <c r="N20" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="O20" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -2358,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="Y20" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2366,46 +2384,46 @@
         <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E21" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F21">
-        <v>1600000</v>
+        <v>6450000</v>
       </c>
       <c r="G21">
-        <v>1600000</v>
+        <v>6450000</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="J21">
-        <v>23500</v>
+        <v>2000</v>
       </c>
       <c r="K21">
-        <v>8751446</v>
+        <v>6930000</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="N21" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="O21" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -2435,84 +2453,161 @@
         <v>0</v>
       </c>
       <c r="Y21" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:25">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" t="s">
+        <v>97</v>
+      </c>
+      <c r="F22">
+        <v>1600000</v>
+      </c>
+      <c r="G22">
+        <v>1600000</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>20000</v>
+      </c>
+      <c r="J22">
+        <v>23500</v>
+      </c>
+      <c r="K22">
+        <v>8751446</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>30000</v>
+      </c>
+      <c r="N22" t="s">
+        <v>119</v>
+      </c>
+      <c r="O22" t="s">
+        <v>135</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
+      <c r="A23" t="s">
         <v>40</v>
       </c>
-      <c r="C22" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" t="s">
-        <v>95</v>
-      </c>
-      <c r="F22">
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" t="s">
+        <v>98</v>
+      </c>
+      <c r="F23">
         <v>23333334</v>
       </c>
-      <c r="G22">
+      <c r="G23">
         <v>23333334</v>
       </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
         <v>3000</v>
       </c>
-      <c r="J22">
+      <c r="J23">
         <v>3800</v>
       </c>
-      <c r="K22">
+      <c r="K23">
         <v>43477664</v>
       </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>3000</v>
       </c>
-      <c r="N22" t="s">
-        <v>116</v>
-      </c>
-      <c r="O22" t="s">
-        <v>118</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>148</v>
+      <c r="N23" t="s">
+        <v>120</v>
+      </c>
+      <c r="O23" t="s">
+        <v>123</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet1.xlsx
+++ b/datasets/sheet1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="147">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -139,36 +139,33 @@
     <t>2024-06-03</t>
   </si>
   <si>
+    <t>2024-08-08</t>
+  </si>
+  <si>
+    <t>2024-08-06</t>
+  </si>
+  <si>
+    <t>2024-07-19</t>
+  </si>
+  <si>
+    <t>2024-07-17</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>2024-06-28</t>
+  </si>
+  <si>
+    <t>2024-06-19</t>
+  </si>
+  <si>
+    <t>2024-06-17</t>
+  </si>
+  <si>
     <t>2024-06-05</t>
   </si>
   <si>
-    <t>2024-05-30</t>
-  </si>
-  <si>
-    <t>2024-08-08</t>
-  </si>
-  <si>
-    <t>2024-08-06</t>
-  </si>
-  <si>
-    <t>2024-07-19</t>
-  </si>
-  <si>
-    <t>2024-07-17</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>2024-06-28</t>
-  </si>
-  <si>
-    <t>2024-06-19</t>
-  </si>
-  <si>
-    <t>2024-06-17</t>
-  </si>
-  <si>
     <t>2024-08-23</t>
   </si>
   <si>
@@ -241,9 +238,6 @@
     <t>엘에스</t>
   </si>
   <si>
-    <t>IBK</t>
-  </si>
-  <si>
     <t>신한, 한국</t>
   </si>
   <si>
@@ -304,12 +298,6 @@
     <t>에스오에스랩</t>
   </si>
   <si>
-    <t>미래에셋비전스팩6호</t>
-  </si>
-  <si>
-    <t>한중엔시에스</t>
-  </si>
-  <si>
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
@@ -370,12 +358,6 @@
     <t>1072.30:1</t>
   </si>
   <si>
-    <t>1,107.2:1</t>
-  </si>
-  <si>
-    <t>725.94:1</t>
-  </si>
-  <si>
     <t>38.7:1</t>
   </si>
   <si>
@@ -421,9 +403,6 @@
     <t>4.19%</t>
   </si>
   <si>
-    <t>12.44%</t>
-  </si>
-  <si>
     <t>첨단바이오의약품 위탁개발생산(CDMO) 서비스 / 차세대 세포,유전자 치료제</t>
   </si>
   <si>
@@ -473,9 +452,6 @@
   </si>
   <si>
     <t>산업용 및 차량용 라이다(LiDAR)</t>
-  </si>
-  <si>
-    <t>수냉식 냉각시스템 ESS Parts, 공랭식 ESS Module Parts, EV Module 및 내연기관 Parts</t>
   </si>
   <si>
     <t>신탁 및 집합투자</t>
@@ -836,7 +812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y23"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -921,16 +897,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F2">
         <v>1566800</v>
@@ -957,10 +933,10 @@
         <v>15300</v>
       </c>
       <c r="N2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="O2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="P2">
         <v>7367362</v>
@@ -990,7 +966,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -998,16 +974,16 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F3">
         <v>1000000</v>
@@ -1034,10 +1010,10 @@
         <v>13000</v>
       </c>
       <c r="N3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="P3">
         <v>25588</v>
@@ -1067,7 +1043,7 @@
         <v>809</v>
       </c>
       <c r="Y3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1075,16 +1051,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F4">
         <v>6500000</v>
@@ -1111,10 +1087,10 @@
         <v>2000</v>
       </c>
       <c r="N4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1144,7 +1120,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1155,13 +1131,13 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F5">
         <v>1400000</v>
@@ -1188,10 +1164,10 @@
         <v>15500</v>
       </c>
       <c r="N5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O5" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="P5">
         <v>10740898602</v>
@@ -1221,7 +1197,7 @@
         <v>219774608</v>
       </c>
       <c r="Y5" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1232,13 +1208,13 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F6">
         <v>1000000</v>
@@ -1265,10 +1241,10 @@
         <v>29000</v>
       </c>
       <c r="N6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="O6" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1298,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1309,13 +1285,13 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F7">
         <v>751000</v>
@@ -1342,10 +1318,10 @@
         <v>21000</v>
       </c>
       <c r="N7" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O7" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1375,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1386,13 +1362,13 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F8">
         <v>5800000</v>
@@ -1419,10 +1395,10 @@
         <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1452,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1463,13 +1439,13 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F9">
         <v>1400000</v>
@@ -1496,10 +1472,10 @@
         <v>16000</v>
       </c>
       <c r="N9" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="O9" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="P9">
         <v>72895458363</v>
@@ -1529,7 +1505,7 @@
         <v>-3801868433</v>
       </c>
       <c r="Y9" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1537,16 +1513,16 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F10">
         <v>2234000</v>
@@ -1573,10 +1549,10 @@
         <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="O10" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="P10">
         <v>1337894447</v>
@@ -1606,7 +1582,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1614,16 +1590,16 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F11">
         <v>1350000</v>
@@ -1650,10 +1626,10 @@
         <v>22000</v>
       </c>
       <c r="N11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="O11" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="P11">
         <v>5214628820</v>
@@ -1683,7 +1659,7 @@
         <v>24178632</v>
       </c>
       <c r="Y11" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1691,16 +1667,16 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F12">
         <v>6000000</v>
@@ -1727,10 +1703,10 @@
         <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O12" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1760,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1768,16 +1744,16 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F13">
         <v>4000000</v>
@@ -1804,10 +1780,10 @@
         <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="O13" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1837,7 +1813,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1845,16 +1821,16 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F14">
         <v>1618000</v>
@@ -1881,10 +1857,10 @@
         <v>10000</v>
       </c>
       <c r="N14" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="O14" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1914,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1922,16 +1898,16 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F15">
         <v>4000000</v>
@@ -1958,10 +1934,10 @@
         <v>2000</v>
       </c>
       <c r="N15" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="O15" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -1991,7 +1967,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1999,16 +1975,16 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F16">
         <v>1810000</v>
@@ -2035,10 +2011,10 @@
         <v>16000</v>
       </c>
       <c r="N16" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="O16" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="P16">
         <v>12596039842</v>
@@ -2068,7 +2044,7 @@
         <v>1795726428</v>
       </c>
       <c r="Y16" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2076,16 +2052,16 @@
         <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F17">
         <v>1330000</v>
@@ -2112,10 +2088,10 @@
         <v>43300</v>
       </c>
       <c r="N17" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="O17" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="P17">
         <v>103267682</v>
@@ -2145,7 +2121,7 @@
         <v>-83246975113</v>
       </c>
       <c r="Y17" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2159,10 +2135,10 @@
         <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F18">
         <v>3400000</v>
@@ -2189,10 +2165,10 @@
         <v>7000</v>
       </c>
       <c r="N18" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="O18" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="P18">
         <v>85187882584</v>
@@ -2222,7 +2198,7 @@
         <v>2646634321</v>
       </c>
       <c r="Y18" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2233,13 +2209,13 @@
         <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E19" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F19">
         <v>6250000</v>
@@ -2266,10 +2242,10 @@
         <v>2000</v>
       </c>
       <c r="N19" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="O19" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -2299,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2310,13 +2286,13 @@
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E20" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F20">
         <v>2000000</v>
@@ -2343,10 +2319,10 @@
         <v>11500</v>
       </c>
       <c r="N20" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="O20" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -2376,54 +2352,54 @@
         <v>0</v>
       </c>
       <c r="Y20" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:25">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F21">
-        <v>6450000</v>
+        <v>23333334</v>
       </c>
       <c r="G21">
-        <v>6450000</v>
+        <v>23333334</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="J21">
-        <v>2000</v>
+        <v>3800</v>
       </c>
       <c r="K21">
-        <v>6930000</v>
+        <v>43477664</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="N21" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="O21" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -2453,161 +2429,7 @@
         <v>0</v>
       </c>
       <c r="Y21" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E22" t="s">
-        <v>97</v>
-      </c>
-      <c r="F22">
-        <v>1600000</v>
-      </c>
-      <c r="G22">
-        <v>1600000</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>20000</v>
-      </c>
-      <c r="J22">
-        <v>23500</v>
-      </c>
-      <c r="K22">
-        <v>8751446</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>30000</v>
-      </c>
-      <c r="N22" t="s">
-        <v>119</v>
-      </c>
-      <c r="O22" t="s">
-        <v>135</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25">
-      <c r="A23" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" t="s">
-        <v>76</v>
-      </c>
-      <c r="E23" t="s">
-        <v>98</v>
-      </c>
-      <c r="F23">
-        <v>23333334</v>
-      </c>
-      <c r="G23">
-        <v>23333334</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>3000</v>
-      </c>
-      <c r="J23">
-        <v>3800</v>
-      </c>
-      <c r="K23">
-        <v>43477664</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>3000</v>
-      </c>
-      <c r="N23" t="s">
-        <v>120</v>
-      </c>
-      <c r="O23" t="s">
-        <v>123</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet1.xlsx
+++ b/datasets/sheet1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="142">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -202,9 +202,6 @@
     <t>2024-06-26</t>
   </si>
   <si>
-    <t>2024-06-25</t>
-  </si>
-  <si>
     <t>2024-07-01</t>
   </si>
   <si>
@@ -295,9 +292,6 @@
     <t>한국제15호스팩</t>
   </si>
   <si>
-    <t>에스오에스랩</t>
-  </si>
-  <si>
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
@@ -355,9 +349,6 @@
     <t>1,073.31:1</t>
   </si>
   <si>
-    <t>1072.30:1</t>
-  </si>
-  <si>
     <t>38.7:1</t>
   </si>
   <si>
@@ -400,9 +391,6 @@
     <t>11.80%</t>
   </si>
   <si>
-    <t>4.19%</t>
-  </si>
-  <si>
     <t>첨단바이오의약품 위탁개발생산(CDMO) 서비스 / 차세대 세포,유전자 치료제</t>
   </si>
   <si>
@@ -449,9 +437,6 @@
   </si>
   <si>
     <t>전동기 및 발전기 (범용모터, 서보모터)</t>
-  </si>
-  <si>
-    <t>산업용 및 차량용 라이다(LiDAR)</t>
   </si>
   <si>
     <t>신탁 및 집합투자</t>
@@ -812,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:Y20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -903,10 +888,10 @@
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F2">
         <v>1566800</v>
@@ -933,10 +918,10 @@
         <v>15300</v>
       </c>
       <c r="N2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="P2">
         <v>7367362</v>
@@ -966,7 +951,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -980,10 +965,10 @@
         <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F3">
         <v>1000000</v>
@@ -1010,10 +995,10 @@
         <v>13000</v>
       </c>
       <c r="N3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="P3">
         <v>25588</v>
@@ -1043,7 +1028,7 @@
         <v>809</v>
       </c>
       <c r="Y3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1057,10 +1042,10 @@
         <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F4">
         <v>6500000</v>
@@ -1087,10 +1072,10 @@
         <v>2000</v>
       </c>
       <c r="N4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="O4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1120,7 +1105,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1134,10 +1119,10 @@
         <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F5">
         <v>1400000</v>
@@ -1164,10 +1149,10 @@
         <v>15500</v>
       </c>
       <c r="N5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="O5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P5">
         <v>10740898602</v>
@@ -1197,7 +1182,7 @@
         <v>219774608</v>
       </c>
       <c r="Y5" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1211,10 +1196,10 @@
         <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F6">
         <v>1000000</v>
@@ -1241,10 +1226,10 @@
         <v>29000</v>
       </c>
       <c r="N6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="O6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1274,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1288,10 +1273,10 @@
         <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F7">
         <v>751000</v>
@@ -1318,10 +1303,10 @@
         <v>21000</v>
       </c>
       <c r="N7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1351,7 +1336,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1365,10 +1350,10 @@
         <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F8">
         <v>5800000</v>
@@ -1395,10 +1380,10 @@
         <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="O8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1428,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1442,10 +1427,10 @@
         <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F9">
         <v>1400000</v>
@@ -1472,10 +1457,10 @@
         <v>16000</v>
       </c>
       <c r="N9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="P9">
         <v>72895458363</v>
@@ -1505,7 +1490,7 @@
         <v>-3801868433</v>
       </c>
       <c r="Y9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1519,10 +1504,10 @@
         <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F10">
         <v>2234000</v>
@@ -1549,10 +1534,10 @@
         <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P10">
         <v>1337894447</v>
@@ -1582,7 +1567,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1596,10 +1581,10 @@
         <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F11">
         <v>1350000</v>
@@ -1626,10 +1611,10 @@
         <v>22000</v>
       </c>
       <c r="N11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="O11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="P11">
         <v>5214628820</v>
@@ -1659,7 +1644,7 @@
         <v>24178632</v>
       </c>
       <c r="Y11" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1673,10 +1658,10 @@
         <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F12">
         <v>6000000</v>
@@ -1703,10 +1688,10 @@
         <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="O12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1736,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1750,10 +1735,10 @@
         <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F13">
         <v>4000000</v>
@@ -1780,10 +1765,10 @@
         <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="O13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1813,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1827,10 +1812,10 @@
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F14">
         <v>1618000</v>
@@ -1857,10 +1842,10 @@
         <v>10000</v>
       </c>
       <c r="N14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="O14" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1890,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1904,10 +1889,10 @@
         <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F15">
         <v>4000000</v>
@@ -1934,10 +1919,10 @@
         <v>2000</v>
       </c>
       <c r="N15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="O15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -1967,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1981,10 +1966,10 @@
         <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F16">
         <v>1810000</v>
@@ -2011,10 +1996,10 @@
         <v>16000</v>
       </c>
       <c r="N16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O16" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="P16">
         <v>12596039842</v>
@@ -2044,7 +2029,7 @@
         <v>1795726428</v>
       </c>
       <c r="Y16" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2058,10 +2043,10 @@
         <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F17">
         <v>1330000</v>
@@ -2088,10 +2073,10 @@
         <v>43300</v>
       </c>
       <c r="N17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O17" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="P17">
         <v>103267682</v>
@@ -2121,7 +2106,7 @@
         <v>-83246975113</v>
       </c>
       <c r="Y17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2135,10 +2120,10 @@
         <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F18">
         <v>3400000</v>
@@ -2165,10 +2150,10 @@
         <v>7000</v>
       </c>
       <c r="N18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O18" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P18">
         <v>85187882584</v>
@@ -2198,7 +2183,7 @@
         <v>2646634321</v>
       </c>
       <c r="Y18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2212,10 +2197,10 @@
         <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F19">
         <v>6250000</v>
@@ -2242,10 +2227,10 @@
         <v>2000</v>
       </c>
       <c r="N19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="O19" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -2275,7 +2260,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2283,46 +2268,46 @@
         <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
         <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F20">
-        <v>2000000</v>
+        <v>23333334</v>
       </c>
       <c r="G20">
-        <v>2000000</v>
+        <v>23333334</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>7500</v>
+        <v>3000</v>
       </c>
       <c r="J20">
-        <v>9000</v>
+        <v>3800</v>
       </c>
       <c r="K20">
-        <v>17529140</v>
+        <v>43477664</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>11500</v>
+        <v>3000</v>
       </c>
       <c r="N20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O20" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -2352,84 +2337,7 @@
         <v>0</v>
       </c>
       <c r="Y20" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" t="s">
-        <v>94</v>
-      </c>
-      <c r="F21">
-        <v>23333334</v>
-      </c>
-      <c r="G21">
-        <v>23333334</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>3000</v>
-      </c>
-      <c r="J21">
-        <v>3800</v>
-      </c>
-      <c r="K21">
-        <v>43477664</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>3000</v>
-      </c>
-      <c r="N21" t="s">
-        <v>114</v>
-      </c>
-      <c r="O21" t="s">
-        <v>117</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet1.xlsx
+++ b/datasets/sheet1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="138">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -133,9 +133,6 @@
     <t>2024-06-07</t>
   </si>
   <si>
-    <t>2024-06-10</t>
-  </si>
-  <si>
     <t>2024-06-03</t>
   </si>
   <si>
@@ -199,9 +196,6 @@
     <t>2024-07-02</t>
   </si>
   <si>
-    <t>2024-06-26</t>
-  </si>
-  <si>
     <t>2024-07-01</t>
   </si>
   <si>
@@ -289,9 +283,6 @@
     <t>하이젠알앤엠</t>
   </si>
   <si>
-    <t>한국제15호스팩</t>
-  </si>
-  <si>
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
@@ -344,9 +335,6 @@
   </si>
   <si>
     <t>1099.21:1</t>
-  </si>
-  <si>
-    <t>1,073.31:1</t>
   </si>
   <si>
     <t>38.7:1</t>
@@ -797,7 +785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y20"/>
+  <dimension ref="A1:Y19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -882,16 +870,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F2">
         <v>1566800</v>
@@ -918,10 +906,10 @@
         <v>15300</v>
       </c>
       <c r="N2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="P2">
         <v>7367362</v>
@@ -951,7 +939,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -959,16 +947,16 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F3">
         <v>1000000</v>
@@ -995,10 +983,10 @@
         <v>13000</v>
       </c>
       <c r="N3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="P3">
         <v>25588</v>
@@ -1028,7 +1016,7 @@
         <v>809</v>
       </c>
       <c r="Y3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1036,16 +1024,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F4">
         <v>6500000</v>
@@ -1072,10 +1060,10 @@
         <v>2000</v>
       </c>
       <c r="N4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1105,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1116,13 +1104,13 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F5">
         <v>1400000</v>
@@ -1149,10 +1137,10 @@
         <v>15500</v>
       </c>
       <c r="N5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="O5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="P5">
         <v>10740898602</v>
@@ -1182,7 +1170,7 @@
         <v>219774608</v>
       </c>
       <c r="Y5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1193,13 +1181,13 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F6">
         <v>1000000</v>
@@ -1226,10 +1214,10 @@
         <v>29000</v>
       </c>
       <c r="N6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1259,7 +1247,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1270,13 +1258,13 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F7">
         <v>751000</v>
@@ -1303,10 +1291,10 @@
         <v>21000</v>
       </c>
       <c r="N7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1336,7 +1324,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1347,13 +1335,13 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F8">
         <v>5800000</v>
@@ -1380,10 +1368,10 @@
         <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1413,7 +1401,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1424,13 +1412,13 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F9">
         <v>1400000</v>
@@ -1457,10 +1445,10 @@
         <v>16000</v>
       </c>
       <c r="N9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O9" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="P9">
         <v>72895458363</v>
@@ -1490,7 +1478,7 @@
         <v>-3801868433</v>
       </c>
       <c r="Y9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1498,16 +1486,16 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F10">
         <v>2234000</v>
@@ -1534,10 +1522,10 @@
         <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="P10">
         <v>1337894447</v>
@@ -1567,7 +1555,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1575,16 +1563,16 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F11">
         <v>1350000</v>
@@ -1611,10 +1599,10 @@
         <v>22000</v>
       </c>
       <c r="N11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="O11" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="P11">
         <v>5214628820</v>
@@ -1644,7 +1632,7 @@
         <v>24178632</v>
       </c>
       <c r="Y11" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1652,16 +1640,16 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F12">
         <v>6000000</v>
@@ -1688,10 +1676,10 @@
         <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="O12" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1721,7 +1709,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1729,16 +1717,16 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F13">
         <v>4000000</v>
@@ -1765,10 +1753,10 @@
         <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O13" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1798,7 +1786,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1806,16 +1794,16 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F14">
         <v>1618000</v>
@@ -1842,10 +1830,10 @@
         <v>10000</v>
       </c>
       <c r="N14" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="O14" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1875,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1883,16 +1871,16 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F15">
         <v>4000000</v>
@@ -1919,10 +1907,10 @@
         <v>2000</v>
       </c>
       <c r="N15" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O15" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -1952,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1960,16 +1948,16 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F16">
         <v>1810000</v>
@@ -1996,10 +1984,10 @@
         <v>16000</v>
       </c>
       <c r="N16" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="O16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="P16">
         <v>12596039842</v>
@@ -2029,7 +2017,7 @@
         <v>1795726428</v>
       </c>
       <c r="Y16" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2037,16 +2025,16 @@
         <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F17">
         <v>1330000</v>
@@ -2073,10 +2061,10 @@
         <v>43300</v>
       </c>
       <c r="N17" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="O17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="P17">
         <v>103267682</v>
@@ -2106,7 +2094,7 @@
         <v>-83246975113</v>
       </c>
       <c r="Y17" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2120,10 +2108,10 @@
         <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F18">
         <v>3400000</v>
@@ -2150,10 +2138,10 @@
         <v>7000</v>
       </c>
       <c r="N18" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="O18" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P18">
         <v>85187882584</v>
@@ -2183,7 +2171,7 @@
         <v>2646634321</v>
       </c>
       <c r="Y18" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2191,47 +2179,47 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F19">
-        <v>6250000</v>
+        <v>23333334</v>
       </c>
       <c r="G19">
-        <v>6250000</v>
+        <v>23333334</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="J19">
-        <v>2000</v>
+        <v>3800</v>
       </c>
       <c r="K19">
-        <v>6870000</v>
+        <v>43477664</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="N19" t="s">
+        <v>107</v>
+      </c>
+      <c r="O19" t="s">
         <v>110</v>
       </c>
-      <c r="O19" t="s">
-        <v>114</v>
-      </c>
       <c r="P19">
         <v>0</v>
       </c>
@@ -2260,84 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25">
-      <c r="A20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" t="s">
-        <v>92</v>
-      </c>
-      <c r="F20">
-        <v>23333334</v>
-      </c>
-      <c r="G20">
-        <v>23333334</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>3000</v>
-      </c>
-      <c r="J20">
-        <v>3800</v>
-      </c>
-      <c r="K20">
-        <v>43477664</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>3000</v>
-      </c>
-      <c r="N20" t="s">
-        <v>111</v>
-      </c>
-      <c r="O20" t="s">
-        <v>114</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet1.xlsx
+++ b/datasets/sheet1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="133">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -130,9 +130,6 @@
     <t>2024-06-11</t>
   </si>
   <si>
-    <t>2024-06-07</t>
-  </si>
-  <si>
     <t>2024-06-03</t>
   </si>
   <si>
@@ -280,9 +277,6 @@
     <t>이노스페이스</t>
   </si>
   <si>
-    <t>하이젠알앤엠</t>
-  </si>
-  <si>
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
@@ -334,9 +328,6 @@
     <t>598.87:1</t>
   </si>
   <si>
-    <t>1099.21:1</t>
-  </si>
-  <si>
     <t>38.7:1</t>
   </si>
   <si>
@@ -376,9 +367,6 @@
     <t>1.99%</t>
   </si>
   <si>
-    <t>11.80%</t>
-  </si>
-  <si>
     <t>첨단바이오의약품 위탁개발생산(CDMO) 서비스 / 차세대 세포,유전자 치료제</t>
   </si>
   <si>
@@ -422,9 +410,6 @@
   </si>
   <si>
     <t>소형발사체, 로켓추진기관, 과학로켓, 시험평가용역</t>
-  </si>
-  <si>
-    <t>전동기 및 발전기 (범용모터, 서보모터)</t>
   </si>
   <si>
     <t>신탁 및 집합투자</t>
@@ -785,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y19"/>
+  <dimension ref="A1:Y18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -870,16 +855,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F2">
         <v>1566800</v>
@@ -906,10 +891,10 @@
         <v>15300</v>
       </c>
       <c r="N2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="P2">
         <v>7367362</v>
@@ -939,7 +924,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -947,16 +932,16 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F3">
         <v>1000000</v>
@@ -983,10 +968,10 @@
         <v>13000</v>
       </c>
       <c r="N3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="O3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="P3">
         <v>25588</v>
@@ -1016,7 +1001,7 @@
         <v>809</v>
       </c>
       <c r="Y3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1024,16 +1009,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F4">
         <v>6500000</v>
@@ -1060,10 +1045,10 @@
         <v>2000</v>
       </c>
       <c r="N4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1093,7 +1078,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1104,13 +1089,13 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F5">
         <v>1400000</v>
@@ -1137,10 +1122,10 @@
         <v>15500</v>
       </c>
       <c r="N5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P5">
         <v>10740898602</v>
@@ -1170,7 +1155,7 @@
         <v>219774608</v>
       </c>
       <c r="Y5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1181,13 +1166,13 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F6">
         <v>1000000</v>
@@ -1214,10 +1199,10 @@
         <v>29000</v>
       </c>
       <c r="N6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1247,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1258,13 +1243,13 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F7">
         <v>751000</v>
@@ -1291,10 +1276,10 @@
         <v>21000</v>
       </c>
       <c r="N7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1324,7 +1309,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1335,13 +1320,13 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F8">
         <v>5800000</v>
@@ -1368,10 +1353,10 @@
         <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1401,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1412,13 +1397,13 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F9">
         <v>1400000</v>
@@ -1445,10 +1430,10 @@
         <v>16000</v>
       </c>
       <c r="N9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="O9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="P9">
         <v>72895458363</v>
@@ -1478,7 +1463,7 @@
         <v>-3801868433</v>
       </c>
       <c r="Y9" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1486,16 +1471,16 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F10">
         <v>2234000</v>
@@ -1522,10 +1507,10 @@
         <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="O10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="P10">
         <v>1337894447</v>
@@ -1555,7 +1540,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1563,16 +1548,16 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F11">
         <v>1350000</v>
@@ -1599,10 +1584,10 @@
         <v>22000</v>
       </c>
       <c r="N11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="O11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="P11">
         <v>5214628820</v>
@@ -1632,7 +1617,7 @@
         <v>24178632</v>
       </c>
       <c r="Y11" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1640,16 +1625,16 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F12">
         <v>6000000</v>
@@ -1676,10 +1661,10 @@
         <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1709,7 +1694,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1717,16 +1702,16 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F13">
         <v>4000000</v>
@@ -1753,10 +1738,10 @@
         <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="O13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1786,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1794,16 +1779,16 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F14">
         <v>1618000</v>
@@ -1830,10 +1815,10 @@
         <v>10000</v>
       </c>
       <c r="N14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="O14" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1863,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1871,16 +1856,16 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F15">
         <v>4000000</v>
@@ -1907,10 +1892,10 @@
         <v>2000</v>
       </c>
       <c r="N15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -1940,7 +1925,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1948,16 +1933,16 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F16">
         <v>1810000</v>
@@ -1984,10 +1969,10 @@
         <v>16000</v>
       </c>
       <c r="N16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="O16" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P16">
         <v>12596039842</v>
@@ -2017,7 +2002,7 @@
         <v>1795726428</v>
       </c>
       <c r="Y16" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2025,16 +2010,16 @@
         <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F17">
         <v>1330000</v>
@@ -2061,10 +2046,10 @@
         <v>43300</v>
       </c>
       <c r="N17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="O17" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="P17">
         <v>103267682</v>
@@ -2094,7 +2079,7 @@
         <v>-83246975113</v>
       </c>
       <c r="Y17" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2102,153 +2087,76 @@
         <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F18">
-        <v>3400000</v>
+        <v>23333334</v>
       </c>
       <c r="G18">
-        <v>3400000</v>
+        <v>23333334</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="J18">
-        <v>5500</v>
+        <v>3800</v>
       </c>
       <c r="K18">
-        <v>30888000</v>
+        <v>43477664</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>7000</v>
+        <v>3000</v>
       </c>
       <c r="N18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="O18" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="P18">
-        <v>85187882584</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>87525689695</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>77247394706</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>2205797752</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>4920387020</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>4336496285</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>1613954566</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>3980493669</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>2646634321</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25">
-      <c r="A19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" t="s">
-        <v>89</v>
-      </c>
-      <c r="F19">
-        <v>23333334</v>
-      </c>
-      <c r="G19">
-        <v>23333334</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>3000</v>
-      </c>
-      <c r="J19">
-        <v>3800</v>
-      </c>
-      <c r="K19">
-        <v>43477664</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>3000</v>
-      </c>
-      <c r="N19" t="s">
-        <v>107</v>
-      </c>
-      <c r="O19" t="s">
-        <v>110</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
-      <c r="W19">
-        <v>0</v>
-      </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet1.xlsx
+++ b/datasets/sheet1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="126">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -130,9 +130,6 @@
     <t>2024-06-11</t>
   </si>
   <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
     <t>2024-08-08</t>
   </si>
   <si>
@@ -157,9 +154,6 @@
     <t>2024-06-17</t>
   </si>
   <si>
-    <t>2024-06-05</t>
-  </si>
-  <si>
     <t>2024-08-23</t>
   </si>
   <si>
@@ -193,9 +187,6 @@
     <t>2024-07-02</t>
   </si>
   <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
     <t>NH</t>
   </si>
   <si>
@@ -226,9 +217,6 @@
     <t>엘에스</t>
   </si>
   <si>
-    <t>신한, 한국</t>
-  </si>
-  <si>
     <t>이엔셀</t>
   </si>
   <si>
@@ -277,9 +265,6 @@
     <t>이노스페이스</t>
   </si>
   <si>
-    <t>신한글로벌액티브리츠</t>
-  </si>
-  <si>
     <t>949.3:1</t>
   </si>
   <si>
@@ -328,9 +313,6 @@
     <t>598.87:1</t>
   </si>
   <si>
-    <t>38.7:1</t>
-  </si>
-  <si>
     <t>0.24%</t>
   </si>
   <si>
@@ -410,9 +392,6 @@
   </si>
   <si>
     <t>소형발사체, 로켓추진기관, 과학로켓, 시험평가용역</t>
-  </si>
-  <si>
-    <t>신탁 및 집합투자</t>
   </si>
 </sst>
 </file>
@@ -770,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y18"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -855,16 +834,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F2">
         <v>1566800</v>
@@ -891,10 +870,10 @@
         <v>15300</v>
       </c>
       <c r="N2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="O2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="P2">
         <v>7367362</v>
@@ -924,7 +903,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -932,16 +911,16 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F3">
         <v>1000000</v>
@@ -968,10 +947,10 @@
         <v>13000</v>
       </c>
       <c r="N3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="O3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="P3">
         <v>25588</v>
@@ -1001,7 +980,7 @@
         <v>809</v>
       </c>
       <c r="Y3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1009,16 +988,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F4">
         <v>6500000</v>
@@ -1045,10 +1024,10 @@
         <v>2000</v>
       </c>
       <c r="N4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="O4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1078,7 +1057,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1089,13 +1068,13 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F5">
         <v>1400000</v>
@@ -1122,10 +1101,10 @@
         <v>15500</v>
       </c>
       <c r="N5" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="O5" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="P5">
         <v>10740898602</v>
@@ -1155,7 +1134,7 @@
         <v>219774608</v>
       </c>
       <c r="Y5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1166,13 +1145,13 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F6">
         <v>1000000</v>
@@ -1199,10 +1178,10 @@
         <v>29000</v>
       </c>
       <c r="N6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="O6" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1232,7 +1211,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1243,13 +1222,13 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F7">
         <v>751000</v>
@@ -1276,10 +1255,10 @@
         <v>21000</v>
       </c>
       <c r="N7" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="O7" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1309,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1320,13 +1299,13 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F8">
         <v>5800000</v>
@@ -1353,10 +1332,10 @@
         <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="O8" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1386,7 +1365,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1397,13 +1376,13 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F9">
         <v>1400000</v>
@@ -1430,10 +1409,10 @@
         <v>16000</v>
       </c>
       <c r="N9" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="O9" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="P9">
         <v>72895458363</v>
@@ -1463,7 +1442,7 @@
         <v>-3801868433</v>
       </c>
       <c r="Y9" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1471,16 +1450,16 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F10">
         <v>2234000</v>
@@ -1507,10 +1486,10 @@
         <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="O10" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="P10">
         <v>1337894447</v>
@@ -1540,7 +1519,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1548,16 +1527,16 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F11">
         <v>1350000</v>
@@ -1584,10 +1563,10 @@
         <v>22000</v>
       </c>
       <c r="N11" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="O11" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="P11">
         <v>5214628820</v>
@@ -1617,7 +1596,7 @@
         <v>24178632</v>
       </c>
       <c r="Y11" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1625,16 +1604,16 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F12">
         <v>6000000</v>
@@ -1661,10 +1640,10 @@
         <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="O12" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1694,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1702,16 +1681,16 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F13">
         <v>4000000</v>
@@ -1738,10 +1717,10 @@
         <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="O13" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1771,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1779,16 +1758,16 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E14" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F14">
         <v>1618000</v>
@@ -1815,10 +1794,10 @@
         <v>10000</v>
       </c>
       <c r="N14" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O14" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1848,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1856,16 +1835,16 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F15">
         <v>4000000</v>
@@ -1892,11 +1871,11 @@
         <v>2000</v>
       </c>
       <c r="N15" t="s">
+        <v>96</v>
+      </c>
+      <c r="O15" t="s">
         <v>101</v>
       </c>
-      <c r="O15" t="s">
-        <v>107</v>
-      </c>
       <c r="P15">
         <v>0</v>
       </c>
@@ -1925,7 +1904,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1933,16 +1912,16 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F16">
         <v>1810000</v>
@@ -1969,10 +1948,10 @@
         <v>16000</v>
       </c>
       <c r="N16" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="O16" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="P16">
         <v>12596039842</v>
@@ -2002,7 +1981,7 @@
         <v>1795726428</v>
       </c>
       <c r="Y16" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2010,16 +1989,16 @@
         <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F17">
         <v>1330000</v>
@@ -2046,10 +2025,10 @@
         <v>43300</v>
       </c>
       <c r="N17" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="O17" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="P17">
         <v>103267682</v>
@@ -2079,84 +2058,7 @@
         <v>-83246975113</v>
       </c>
       <c r="Y17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25">
-      <c r="A18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" t="s">
-        <v>70</v>
-      </c>
-      <c r="E18" t="s">
-        <v>87</v>
-      </c>
-      <c r="F18">
-        <v>23333334</v>
-      </c>
-      <c r="G18">
-        <v>23333334</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>3000</v>
-      </c>
-      <c r="J18">
-        <v>3800</v>
-      </c>
-      <c r="K18">
-        <v>43477664</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>3000</v>
-      </c>
-      <c r="N18" t="s">
-        <v>104</v>
-      </c>
-      <c r="O18" t="s">
-        <v>107</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>0</v>
-      </c>
-      <c r="V18">
-        <v>0</v>
-      </c>
-      <c r="W18">
-        <v>0</v>
-      </c>
-      <c r="X18">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet1.xlsx
+++ b/datasets/sheet1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="119">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -127,9 +127,6 @@
     <t>2024-06-13</t>
   </si>
   <si>
-    <t>2024-06-11</t>
-  </si>
-  <si>
     <t>2024-08-08</t>
   </si>
   <si>
@@ -151,9 +148,6 @@
     <t>2024-06-19</t>
   </si>
   <si>
-    <t>2024-06-17</t>
-  </si>
-  <si>
     <t>2024-08-23</t>
   </si>
   <si>
@@ -184,9 +178,6 @@
     <t>2024-07-03</t>
   </si>
   <si>
-    <t>2024-07-02</t>
-  </si>
-  <si>
     <t>NH</t>
   </si>
   <si>
@@ -262,9 +253,6 @@
     <t>하스</t>
   </si>
   <si>
-    <t>이노스페이스</t>
-  </si>
-  <si>
     <t>949.3:1</t>
   </si>
   <si>
@@ -310,9 +298,6 @@
     <t>946.40:1</t>
   </si>
   <si>
-    <t>598.87:1</t>
-  </si>
-  <si>
     <t>0.24%</t>
   </si>
   <si>
@@ -346,9 +331,6 @@
     <t>6.36%</t>
   </si>
   <si>
-    <t>1.99%</t>
-  </si>
-  <si>
     <t>첨단바이오의약품 위탁개발생산(CDMO) 서비스 / 차세대 세포,유전자 치료제</t>
   </si>
   <si>
@@ -389,9 +371,6 @@
   </si>
   <si>
     <t>리튬디실리케이트 수복소재(Amber block, Amber Ingot 등), 지르코니아 유치관</t>
-  </si>
-  <si>
-    <t>소형발사체, 로켓추진기관, 과학로켓, 시험평가용역</t>
   </si>
 </sst>
 </file>
@@ -749,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y17"/>
+  <dimension ref="A1:Y16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -834,16 +813,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F2">
         <v>1566800</v>
@@ -870,10 +849,10 @@
         <v>15300</v>
       </c>
       <c r="N2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="P2">
         <v>7367362</v>
@@ -903,7 +882,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -911,16 +890,16 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F3">
         <v>1000000</v>
@@ -947,10 +926,10 @@
         <v>13000</v>
       </c>
       <c r="N3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="O3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P3">
         <v>25588</v>
@@ -980,7 +959,7 @@
         <v>809</v>
       </c>
       <c r="Y3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -988,16 +967,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F4">
         <v>6500000</v>
@@ -1024,10 +1003,10 @@
         <v>2000</v>
       </c>
       <c r="N4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1057,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1068,13 +1047,13 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F5">
         <v>1400000</v>
@@ -1101,10 +1080,10 @@
         <v>15500</v>
       </c>
       <c r="N5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="O5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="P5">
         <v>10740898602</v>
@@ -1134,7 +1113,7 @@
         <v>219774608</v>
       </c>
       <c r="Y5" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1145,13 +1124,13 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F6">
         <v>1000000</v>
@@ -1178,10 +1157,10 @@
         <v>29000</v>
       </c>
       <c r="N6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="O6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1211,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1222,13 +1201,13 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F7">
         <v>751000</v>
@@ -1255,10 +1234,10 @@
         <v>21000</v>
       </c>
       <c r="N7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="O7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1288,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1299,13 +1278,13 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F8">
         <v>5800000</v>
@@ -1332,10 +1311,10 @@
         <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="O8" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1365,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1376,13 +1355,13 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F9">
         <v>1400000</v>
@@ -1409,10 +1388,10 @@
         <v>16000</v>
       </c>
       <c r="N9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="O9" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="P9">
         <v>72895458363</v>
@@ -1442,7 +1421,7 @@
         <v>-3801868433</v>
       </c>
       <c r="Y9" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1450,16 +1429,16 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F10">
         <v>2234000</v>
@@ -1486,10 +1465,10 @@
         <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="O10" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="P10">
         <v>1337894447</v>
@@ -1519,7 +1498,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1527,16 +1506,16 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F11">
         <v>1350000</v>
@@ -1563,10 +1542,10 @@
         <v>22000</v>
       </c>
       <c r="N11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="P11">
         <v>5214628820</v>
@@ -1596,7 +1575,7 @@
         <v>24178632</v>
       </c>
       <c r="Y11" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1604,16 +1583,16 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F12">
         <v>6000000</v>
@@ -1640,10 +1619,10 @@
         <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="O12" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1673,7 +1652,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1681,16 +1660,16 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F13">
         <v>4000000</v>
@@ -1717,10 +1696,10 @@
         <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="O13" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1750,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1758,16 +1737,16 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F14">
         <v>1618000</v>
@@ -1794,10 +1773,10 @@
         <v>10000</v>
       </c>
       <c r="N14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="O14" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1827,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1835,16 +1814,16 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F15">
         <v>4000000</v>
@@ -1871,11 +1850,11 @@
         <v>2000</v>
       </c>
       <c r="N15" t="s">
+        <v>92</v>
+      </c>
+      <c r="O15" t="s">
         <v>96</v>
       </c>
-      <c r="O15" t="s">
-        <v>101</v>
-      </c>
       <c r="P15">
         <v>0</v>
       </c>
@@ -1904,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1912,16 +1891,16 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E16" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F16">
         <v>1810000</v>
@@ -1948,10 +1927,10 @@
         <v>16000</v>
       </c>
       <c r="N16" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="O16" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="P16">
         <v>12596039842</v>
@@ -1981,84 +1960,7 @@
         <v>1795726428</v>
       </c>
       <c r="Y16" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25">
-      <c r="A17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" t="s">
-        <v>82</v>
-      </c>
-      <c r="F17">
-        <v>1330000</v>
-      </c>
-      <c r="G17">
-        <v>1330000</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>36400</v>
-      </c>
-      <c r="J17">
-        <v>43300</v>
-      </c>
-      <c r="K17">
-        <v>9375694</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>43300</v>
-      </c>
-      <c r="N17" t="s">
-        <v>98</v>
-      </c>
-      <c r="O17" t="s">
-        <v>110</v>
-      </c>
-      <c r="P17">
-        <v>103267682</v>
-      </c>
-      <c r="Q17">
-        <v>342201581</v>
-      </c>
-      <c r="R17">
-        <v>231425455</v>
-      </c>
-      <c r="S17">
-        <v>-7598692896</v>
-      </c>
-      <c r="T17">
-        <v>-25822444575</v>
-      </c>
-      <c r="U17">
-        <v>-15929213281</v>
-      </c>
-      <c r="V17">
-        <v>-6973258680</v>
-      </c>
-      <c r="W17">
-        <v>-48433907514</v>
-      </c>
-      <c r="X17">
-        <v>-83246975113</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet1.xlsx
+++ b/datasets/sheet1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="112">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -124,9 +124,6 @@
     <t>2024-06-27</t>
   </si>
   <si>
-    <t>2024-06-13</t>
-  </si>
-  <si>
     <t>2024-08-08</t>
   </si>
   <si>
@@ -145,9 +142,6 @@
     <t>2024-06-28</t>
   </si>
   <si>
-    <t>2024-06-19</t>
-  </si>
-  <si>
     <t>2024-08-23</t>
   </si>
   <si>
@@ -175,9 +169,6 @@
     <t>2024-07-12</t>
   </si>
   <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
     <t>NH</t>
   </si>
   <si>
@@ -250,9 +241,6 @@
     <t>이베스트스팩6호</t>
   </si>
   <si>
-    <t>하스</t>
-  </si>
-  <si>
     <t>949.3:1</t>
   </si>
   <si>
@@ -295,9 +283,6 @@
     <t>1131.75:1</t>
   </si>
   <si>
-    <t>946.40:1</t>
-  </si>
-  <si>
     <t>0.24%</t>
   </si>
   <si>
@@ -328,9 +313,6 @@
     <t>4.50%</t>
   </si>
   <si>
-    <t>6.36%</t>
-  </si>
-  <si>
     <t>첨단바이오의약품 위탁개발생산(CDMO) 서비스 / 차세대 세포,유전자 치료제</t>
   </si>
   <si>
@@ -368,9 +350,6 @@
   </si>
   <si>
     <t>CellCor SFD/CD(세포배양배지)</t>
-  </si>
-  <si>
-    <t>리튬디실리케이트 수복소재(Amber block, Amber Ingot 등), 지르코니아 유치관</t>
   </si>
 </sst>
 </file>
@@ -728,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y16"/>
+  <dimension ref="A1:Y15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -813,16 +792,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F2">
         <v>1566800</v>
@@ -849,10 +828,10 @@
         <v>15300</v>
       </c>
       <c r="N2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="O2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="P2">
         <v>7367362</v>
@@ -882,7 +861,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -890,16 +869,16 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F3">
         <v>1000000</v>
@@ -926,10 +905,10 @@
         <v>13000</v>
       </c>
       <c r="N3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="O3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="P3">
         <v>25588</v>
@@ -959,7 +938,7 @@
         <v>809</v>
       </c>
       <c r="Y3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -967,16 +946,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F4">
         <v>6500000</v>
@@ -1003,10 +982,10 @@
         <v>2000</v>
       </c>
       <c r="N4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="O4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1036,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1047,13 +1026,13 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F5">
         <v>1400000</v>
@@ -1080,10 +1059,10 @@
         <v>15500</v>
       </c>
       <c r="N5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="O5" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="P5">
         <v>10740898602</v>
@@ -1113,7 +1092,7 @@
         <v>219774608</v>
       </c>
       <c r="Y5" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1124,13 +1103,13 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F6">
         <v>1000000</v>
@@ -1157,10 +1136,10 @@
         <v>29000</v>
       </c>
       <c r="N6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1190,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1201,13 +1180,13 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F7">
         <v>751000</v>
@@ -1234,10 +1213,10 @@
         <v>21000</v>
       </c>
       <c r="N7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="O7" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1267,7 +1246,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1278,13 +1257,13 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F8">
         <v>5800000</v>
@@ -1311,10 +1290,10 @@
         <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O8" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1344,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1355,13 +1334,13 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F9">
         <v>1400000</v>
@@ -1388,10 +1367,10 @@
         <v>16000</v>
       </c>
       <c r="N9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="O9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P9">
         <v>72895458363</v>
@@ -1421,7 +1400,7 @@
         <v>-3801868433</v>
       </c>
       <c r="Y9" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1429,16 +1408,16 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F10">
         <v>2234000</v>
@@ -1465,10 +1444,10 @@
         <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="O10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="P10">
         <v>1337894447</v>
@@ -1498,7 +1477,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1506,16 +1485,16 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F11">
         <v>1350000</v>
@@ -1542,10 +1521,10 @@
         <v>22000</v>
       </c>
       <c r="N11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="O11" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="P11">
         <v>5214628820</v>
@@ -1575,7 +1554,7 @@
         <v>24178632</v>
       </c>
       <c r="Y11" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1583,16 +1562,16 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
         <v>51</v>
       </c>
-      <c r="D12" t="s">
-        <v>54</v>
-      </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F12">
         <v>6000000</v>
@@ -1619,10 +1598,10 @@
         <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="O12" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1652,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1660,16 +1639,16 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F13">
         <v>4000000</v>
@@ -1696,10 +1675,10 @@
         <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="O13" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1729,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1737,16 +1716,16 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F14">
         <v>1618000</v>
@@ -1773,10 +1752,10 @@
         <v>10000</v>
       </c>
       <c r="N14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="O14" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1806,7 +1785,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1814,16 +1793,16 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F15">
         <v>4000000</v>
@@ -1850,10 +1829,10 @@
         <v>2000</v>
       </c>
       <c r="N15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O15" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -1883,84 +1862,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25">
-      <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16">
-        <v>1810000</v>
-      </c>
-      <c r="G16">
-        <v>1810000</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>9000</v>
-      </c>
-      <c r="J16">
-        <v>12000</v>
-      </c>
-      <c r="K16">
-        <v>7836009</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>16000</v>
-      </c>
-      <c r="N16" t="s">
-        <v>93</v>
-      </c>
-      <c r="O16" t="s">
-        <v>104</v>
-      </c>
-      <c r="P16">
-        <v>12596039842</v>
-      </c>
-      <c r="Q16">
-        <v>14910346438</v>
-      </c>
-      <c r="R16">
-        <v>16039074617</v>
-      </c>
-      <c r="S16">
-        <v>1732604466</v>
-      </c>
-      <c r="T16">
-        <v>2893667787</v>
-      </c>
-      <c r="U16">
-        <v>1613779678</v>
-      </c>
-      <c r="V16">
-        <v>1558081149</v>
-      </c>
-      <c r="W16">
-        <v>2643467726</v>
-      </c>
-      <c r="X16">
-        <v>1795726428</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet1.xlsx
+++ b/datasets/sheet1.xlsx
@@ -91,6 +91,9 @@
     <t>주요제품</t>
   </si>
   <si>
+    <t>2024-08-26</t>
+  </si>
+  <si>
     <t>2024-08-02</t>
   </si>
   <si>
@@ -121,7 +124,7 @@
     <t>2024-06-24</t>
   </si>
   <si>
-    <t>2024-06-27</t>
+    <t>2024-08-27</t>
   </si>
   <si>
     <t>2024-08-08</t>
@@ -142,6 +145,9 @@
     <t>2024-06-28</t>
   </si>
   <si>
+    <t>2024-09-11</t>
+  </si>
+  <si>
     <t>2024-08-23</t>
   </si>
   <si>
@@ -166,7 +172,7 @@
     <t>2024-07-26</t>
   </si>
   <si>
-    <t>2024-07-12</t>
+    <t>미래</t>
   </si>
   <si>
     <t>NH</t>
@@ -187,16 +193,13 @@
     <t>교보</t>
   </si>
   <si>
-    <t>미래</t>
-  </si>
-  <si>
     <t>삼성</t>
   </si>
   <si>
     <t>SK</t>
   </si>
   <si>
-    <t>엘에스</t>
+    <t>미래에셋비전스팩7호</t>
   </si>
   <si>
     <t>이엔셀</t>
@@ -238,7 +241,7 @@
     <t>엑셀세라퓨틱스</t>
   </si>
   <si>
-    <t>이베스트스팩6호</t>
+    <t>1051.62 :1</t>
   </si>
   <si>
     <t>949.3:1</t>
@@ -280,7 +283,7 @@
     <t>1233.80:1</t>
   </si>
   <si>
-    <t>1131.75:1</t>
+    <t>-</t>
   </si>
   <si>
     <t>0.24%</t>
@@ -289,9 +292,6 @@
     <t>4.23%</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>1.03%</t>
   </si>
   <si>
@@ -313,6 +313,9 @@
     <t>4.50%</t>
   </si>
   <si>
+    <t>기업인수합병</t>
+  </si>
+  <si>
     <t>첨단바이오의약품 위탁개발생산(CDMO) 서비스 / 차세대 세포,유전자 치료제</t>
   </si>
   <si>
@@ -329,9 +332,6 @@
   </si>
   <si>
     <t>모바일 앱 개발 플랫폼</t>
-  </si>
-  <si>
-    <t>기업인수합병</t>
   </si>
   <si>
     <t>국내외 은행 및 금융기업 대상 코어뱅킹 소프트웨어</t>
@@ -795,37 +795,37 @@
         <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>61</v>
       </c>
       <c r="F2">
-        <v>1566800</v>
+        <v>7950000</v>
       </c>
       <c r="G2">
-        <v>1566800</v>
+        <v>7950000</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>13600</v>
+        <v>2000</v>
       </c>
       <c r="J2">
-        <v>15300</v>
+        <v>2000</v>
       </c>
       <c r="K2">
-        <v>9349954</v>
+        <v>8215000</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>15300</v>
+        <v>2000</v>
       </c>
       <c r="N2" t="s">
         <v>75</v>
@@ -834,31 +834,31 @@
         <v>89</v>
       </c>
       <c r="P2">
-        <v>7367362</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>10525887</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>1790340</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>-9315442</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>-11755057</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>-2929307</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>-45566953</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>-5053520</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>-2903334</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="s">
         <v>99</v>
@@ -872,37 +872,37 @@
         <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
         <v>62</v>
       </c>
       <c r="F3">
-        <v>1000000</v>
+        <v>1566800</v>
       </c>
       <c r="G3">
-        <v>500000</v>
+        <v>1566800</v>
       </c>
       <c r="H3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>9500</v>
+        <v>13600</v>
       </c>
       <c r="J3">
-        <v>10700</v>
+        <v>15300</v>
       </c>
       <c r="K3">
-        <v>5530000</v>
+        <v>9349954</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>13000</v>
+        <v>15300</v>
       </c>
       <c r="N3" t="s">
         <v>76</v>
@@ -911,31 +911,31 @@
         <v>90</v>
       </c>
       <c r="P3">
-        <v>25588</v>
+        <v>7367362</v>
       </c>
       <c r="Q3">
-        <v>30049</v>
+        <v>10525887</v>
       </c>
       <c r="R3">
-        <v>7363</v>
+        <v>1790340</v>
       </c>
       <c r="S3">
-        <v>3780</v>
+        <v>-9315442</v>
       </c>
       <c r="T3">
-        <v>5016</v>
+        <v>-11755057</v>
       </c>
       <c r="U3">
-        <v>938</v>
+        <v>-2929307</v>
       </c>
       <c r="V3">
-        <v>3456</v>
+        <v>-45566953</v>
       </c>
       <c r="W3">
-        <v>4688</v>
+        <v>-5053520</v>
       </c>
       <c r="X3">
-        <v>809</v>
+        <v>-2903334</v>
       </c>
       <c r="Y3" t="s">
         <v>100</v>
@@ -946,40 +946,40 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
         <v>63</v>
       </c>
       <c r="F4">
-        <v>6500000</v>
+        <v>1000000</v>
       </c>
       <c r="G4">
-        <v>6500000</v>
+        <v>500000</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="I4">
-        <v>2000</v>
+        <v>9500</v>
       </c>
       <c r="J4">
-        <v>2000</v>
+        <v>10700</v>
       </c>
       <c r="K4">
-        <v>7910000</v>
+        <v>5530000</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="N4" t="s">
         <v>77</v>
@@ -988,31 +988,31 @@
         <v>91</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>25588</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>30049</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>7363</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>3780</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>5016</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>938</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>3456</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>4688</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>809</v>
       </c>
       <c r="Y4" t="s">
         <v>101</v>
@@ -1023,73 +1023,73 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
         <v>64</v>
       </c>
       <c r="F5">
-        <v>1400000</v>
+        <v>6500000</v>
       </c>
       <c r="G5">
-        <v>1400000</v>
+        <v>6500000</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>12500</v>
+        <v>2000</v>
       </c>
       <c r="J5">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="K5">
-        <v>7486442</v>
+        <v>7910000</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="N5" t="s">
         <v>78</v>
       </c>
       <c r="O5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="P5">
-        <v>10740898602</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>13058877126</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>3506428302</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1748628548</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>1115790858</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>191527654</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>1491084554</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>1185231988</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>219774608</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="s">
         <v>102</v>
@@ -1100,73 +1100,73 @@
         <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>65</v>
       </c>
       <c r="F6">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="G6">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>24000</v>
+        <v>12500</v>
       </c>
       <c r="J6">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="K6">
-        <v>8008066</v>
+        <v>7486442</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="N6" t="s">
         <v>79</v>
       </c>
       <c r="O6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>10740898602</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>13058877126</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>3506428302</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1748628548</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1115790858</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>191527654</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1491084554</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1185231988</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>219774608</v>
       </c>
       <c r="Y6" t="s">
         <v>103</v>
@@ -1174,49 +1174,49 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s">
         <v>66</v>
       </c>
       <c r="F7">
-        <v>751000</v>
+        <v>1000000</v>
       </c>
       <c r="G7">
-        <v>203700</v>
+        <v>1000000</v>
       </c>
       <c r="H7">
-        <v>547300</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="J7">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="K7">
-        <v>4330068</v>
+        <v>8008066</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="N7" t="s">
         <v>80</v>
       </c>
       <c r="O7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1251,49 +1251,49 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
         <v>67</v>
       </c>
       <c r="F8">
-        <v>5800000</v>
+        <v>751000</v>
       </c>
       <c r="G8">
-        <v>5800000</v>
+        <v>203700</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>547300</v>
       </c>
       <c r="I8">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="J8">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="K8">
-        <v>6100000</v>
+        <v>4330068</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="N8" t="s">
         <v>81</v>
       </c>
       <c r="O8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1334,73 +1334,73 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
         <v>68</v>
       </c>
       <c r="F9">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="G9">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="J9">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="K9">
-        <v>10000988</v>
+        <v>6100000</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N9" t="s">
         <v>82</v>
       </c>
       <c r="O9" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="P9">
-        <v>72895458363</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>72913766913</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>11230711680</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>-6524077412</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>-4556157069</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>-3633759729</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>-11528915410</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>-7978634776</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>-3801868433</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1408,76 +1408,76 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
         <v>69</v>
       </c>
       <c r="F10">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="G10">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J10">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K10">
-        <v>14965620</v>
+        <v>10000988</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N10" t="s">
         <v>83</v>
       </c>
       <c r="O10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P10">
-        <v>1337894447</v>
+        <v>72895458363</v>
       </c>
       <c r="Q10">
-        <v>4495088983</v>
+        <v>72913766913</v>
       </c>
       <c r="R10">
-        <v>99398351</v>
+        <v>11230711680</v>
       </c>
       <c r="S10">
-        <v>-3330678562</v>
+        <v>-6524077412</v>
       </c>
       <c r="T10">
-        <v>-2905069801</v>
+        <v>-4556157069</v>
       </c>
       <c r="U10">
-        <v>-1314068310</v>
+        <v>-3633759729</v>
       </c>
       <c r="V10">
-        <v>-9735376868</v>
+        <v>-11528915410</v>
       </c>
       <c r="W10">
-        <v>-5043515600</v>
+        <v>-7978634776</v>
       </c>
       <c r="X10">
-        <v>-1257080998</v>
+        <v>-3801868433</v>
       </c>
       <c r="Y10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1488,73 +1488,73 @@
         <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
         <v>70</v>
       </c>
       <c r="F11">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="G11">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>14000</v>
+        <v>7300</v>
       </c>
       <c r="J11">
-        <v>17000</v>
+        <v>8500</v>
       </c>
       <c r="K11">
-        <v>6471740</v>
+        <v>14965620</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="N11" t="s">
         <v>84</v>
       </c>
       <c r="O11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P11">
-        <v>5214628820</v>
+        <v>1337894447</v>
       </c>
       <c r="Q11">
-        <v>6009352447</v>
+        <v>4495088983</v>
       </c>
       <c r="R11">
-        <v>965797975</v>
+        <v>99398351</v>
       </c>
       <c r="S11">
-        <v>2015081728</v>
+        <v>-3330678562</v>
       </c>
       <c r="T11">
-        <v>1319755337</v>
+        <v>-2905069801</v>
       </c>
       <c r="U11">
-        <v>-44547594</v>
+        <v>-1314068310</v>
       </c>
       <c r="V11">
-        <v>1503069100</v>
+        <v>-9735376868</v>
       </c>
       <c r="W11">
-        <v>1410469786</v>
+        <v>-5043515600</v>
       </c>
       <c r="X11">
-        <v>24178632</v>
+        <v>-1257080998</v>
       </c>
       <c r="Y11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1565,96 +1565,96 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
         <v>71</v>
       </c>
       <c r="F12">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="G12">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>2000</v>
+        <v>14000</v>
       </c>
       <c r="J12">
-        <v>2000</v>
+        <v>17000</v>
       </c>
       <c r="K12">
-        <v>6345000</v>
+        <v>6471740</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>2000</v>
+        <v>22000</v>
       </c>
       <c r="N12" t="s">
         <v>85</v>
       </c>
       <c r="O12" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>5214628820</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>6009352447</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>965797975</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2015081728</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1319755337</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>-44547594</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1503069100</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1410469786</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>24178632</v>
       </c>
       <c r="Y12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E13" t="s">
         <v>72</v>
       </c>
       <c r="F13">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="G13">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -1666,7 +1666,7 @@
         <v>2000</v>
       </c>
       <c r="K13">
-        <v>4420000</v>
+        <v>6345000</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>86</v>
       </c>
       <c r="O13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1708,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1719,43 +1719,43 @@
         <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
         <v>73</v>
       </c>
       <c r="F14">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="G14">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>6200</v>
+        <v>2000</v>
       </c>
       <c r="J14">
-        <v>7700</v>
+        <v>2000</v>
       </c>
       <c r="K14">
-        <v>10830212</v>
+        <v>4420000</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N14" t="s">
         <v>87</v>
       </c>
       <c r="O14" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1785,7 +1785,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1793,46 +1793,46 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
         <v>74</v>
       </c>
       <c r="F15">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="G15">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>2000</v>
+        <v>6200</v>
       </c>
       <c r="J15">
-        <v>2000</v>
+        <v>7700</v>
       </c>
       <c r="K15">
-        <v>5020000</v>
+        <v>10830212</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="N15" t="s">
         <v>88</v>
       </c>
       <c r="O15" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -1862,7 +1862,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet1.xlsx
+++ b/datasets/sheet1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="106">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -121,9 +121,6 @@
     <t>2024-07-09</t>
   </si>
   <si>
-    <t>2024-06-24</t>
-  </si>
-  <si>
     <t>2024-08-27</t>
   </si>
   <si>
@@ -142,9 +139,6 @@
     <t>2024-07-10</t>
   </si>
   <si>
-    <t>2024-06-28</t>
-  </si>
-  <si>
     <t>2024-09-11</t>
   </si>
   <si>
@@ -238,9 +232,6 @@
     <t>SK증권제13호스팩</t>
   </si>
   <si>
-    <t>엑셀세라퓨틱스</t>
-  </si>
-  <si>
     <t>1051.62 :1</t>
   </si>
   <si>
@@ -280,9 +271,6 @@
     <t>1197.45:1</t>
   </si>
   <si>
-    <t>1233.80:1</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -310,9 +298,6 @@
     <t>5.60%</t>
   </si>
   <si>
-    <t>4.50%</t>
-  </si>
-  <si>
     <t>기업인수합병</t>
   </si>
   <si>
@@ -347,9 +332,6 @@
   </si>
   <si>
     <t>기업인수목적 주식회사</t>
-  </si>
-  <si>
-    <t>CellCor SFD/CD(세포배양배지)</t>
   </si>
 </sst>
 </file>
@@ -707,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y15"/>
+  <dimension ref="A1:Y14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -792,16 +774,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F2">
         <v>7950000</v>
@@ -828,10 +810,10 @@
         <v>2000</v>
       </c>
       <c r="N2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -861,7 +843,7 @@
         <v>0</v>
       </c>
       <c r="Y2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -869,16 +851,16 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F3">
         <v>1566800</v>
@@ -905,10 +887,10 @@
         <v>15300</v>
       </c>
       <c r="N3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="P3">
         <v>7367362</v>
@@ -938,7 +920,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -946,16 +928,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F4">
         <v>1000000</v>
@@ -982,10 +964,10 @@
         <v>13000</v>
       </c>
       <c r="N4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="P4">
         <v>25588</v>
@@ -1015,7 +997,7 @@
         <v>809</v>
       </c>
       <c r="Y4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1023,16 +1005,16 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F5">
         <v>6500000</v>
@@ -1059,10 +1041,10 @@
         <v>2000</v>
       </c>
       <c r="N5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="O5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1092,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="Y5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1103,13 +1085,13 @@
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F6">
         <v>1400000</v>
@@ -1136,10 +1118,10 @@
         <v>15500</v>
       </c>
       <c r="N6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="O6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="P6">
         <v>10740898602</v>
@@ -1169,7 +1151,7 @@
         <v>219774608</v>
       </c>
       <c r="Y6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1180,13 +1162,13 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F7">
         <v>1000000</v>
@@ -1213,10 +1195,10 @@
         <v>29000</v>
       </c>
       <c r="N7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="O7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1246,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1257,13 +1239,13 @@
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F8">
         <v>751000</v>
@@ -1290,10 +1272,10 @@
         <v>21000</v>
       </c>
       <c r="N8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="O8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1323,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1334,13 +1316,13 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F9">
         <v>5800000</v>
@@ -1367,10 +1349,10 @@
         <v>2000</v>
       </c>
       <c r="N9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="O9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1400,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1411,13 +1393,13 @@
         <v>30</v>
       </c>
       <c r="C10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" t="s">
         <v>50</v>
       </c>
-      <c r="D10" t="s">
-        <v>52</v>
-      </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F10">
         <v>1400000</v>
@@ -1444,10 +1426,10 @@
         <v>16000</v>
       </c>
       <c r="N10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="O10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="P10">
         <v>72895458363</v>
@@ -1477,7 +1459,7 @@
         <v>-3801868433</v>
       </c>
       <c r="Y10" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1485,16 +1467,16 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F11">
         <v>2234000</v>
@@ -1521,10 +1503,10 @@
         <v>10000</v>
       </c>
       <c r="N11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O11" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="P11">
         <v>1337894447</v>
@@ -1554,7 +1536,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1562,16 +1544,16 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F12">
         <v>1350000</v>
@@ -1598,10 +1580,10 @@
         <v>22000</v>
       </c>
       <c r="N12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="O12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="P12">
         <v>5214628820</v>
@@ -1631,7 +1613,7 @@
         <v>24178632</v>
       </c>
       <c r="Y12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1639,16 +1621,16 @@
         <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" t="s">
         <v>51</v>
       </c>
-      <c r="D13" t="s">
-        <v>53</v>
-      </c>
       <c r="E13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F13">
         <v>6000000</v>
@@ -1675,10 +1657,10 @@
         <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="O13" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1708,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1716,16 +1698,16 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F14">
         <v>4000000</v>
@@ -1752,10 +1734,10 @@
         <v>2000</v>
       </c>
       <c r="N14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O14" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1785,84 +1767,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15">
-        <v>1618000</v>
-      </c>
-      <c r="G15">
-        <v>1618000</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>6200</v>
-      </c>
-      <c r="J15">
-        <v>7700</v>
-      </c>
-      <c r="K15">
-        <v>10830212</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>10000</v>
-      </c>
-      <c r="N15" t="s">
-        <v>88</v>
-      </c>
-      <c r="O15" t="s">
-        <v>98</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet1.xlsx
+++ b/datasets/sheet1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="100">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -115,9 +115,6 @@
     <t>2024-07-15</t>
   </si>
   <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
     <t>2024-07-09</t>
   </si>
   <si>
@@ -133,9 +130,6 @@
     <t>2024-07-19</t>
   </si>
   <si>
-    <t>2024-07-17</t>
-  </si>
-  <si>
     <t>2024-07-10</t>
   </si>
   <si>
@@ -223,9 +217,6 @@
     <t>아이빔테크놀로지</t>
   </si>
   <si>
-    <t>피앤에스미캐닉스</t>
-  </si>
-  <si>
     <t>엔에이치스팩31호</t>
   </si>
   <si>
@@ -262,9 +253,6 @@
     <t>1011.50:1</t>
   </si>
   <si>
-    <t>986.08:1</t>
-  </si>
-  <si>
     <t>1123.43 :1</t>
   </si>
   <si>
@@ -295,9 +283,6 @@
     <t>0.49%</t>
   </si>
   <si>
-    <t>5.60%</t>
-  </si>
-  <si>
     <t>기업인수합병</t>
   </si>
   <si>
@@ -323,9 +308,6 @@
   </si>
   <si>
     <t>생체현미경, CRO 서비스</t>
-  </si>
-  <si>
-    <t>보행재활로봇 시스템</t>
   </si>
   <si>
     <t>금융지원서비스업</t>
@@ -689,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y14"/>
+  <dimension ref="A1:Y13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -774,16 +756,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F2">
         <v>7950000</v>
@@ -810,10 +792,10 @@
         <v>2000</v>
       </c>
       <c r="N2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="O2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -843,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="Y2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -851,16 +833,16 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F3">
         <v>1566800</v>
@@ -887,10 +869,10 @@
         <v>15300</v>
       </c>
       <c r="N3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="O3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="P3">
         <v>7367362</v>
@@ -920,7 +902,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -928,16 +910,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F4">
         <v>1000000</v>
@@ -964,10 +946,10 @@
         <v>13000</v>
       </c>
       <c r="N4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="O4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="P4">
         <v>25588</v>
@@ -997,7 +979,7 @@
         <v>809</v>
       </c>
       <c r="Y4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1005,16 +987,16 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F5">
         <v>6500000</v>
@@ -1041,10 +1023,10 @@
         <v>2000</v>
       </c>
       <c r="N5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1074,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="Y5" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1085,13 +1067,13 @@
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F6">
         <v>1400000</v>
@@ -1118,10 +1100,10 @@
         <v>15500</v>
       </c>
       <c r="N6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="P6">
         <v>10740898602</v>
@@ -1151,7 +1133,7 @@
         <v>219774608</v>
       </c>
       <c r="Y6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1162,13 +1144,13 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F7">
         <v>1000000</v>
@@ -1195,10 +1177,10 @@
         <v>29000</v>
       </c>
       <c r="N7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1228,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1239,13 +1221,13 @@
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F8">
         <v>751000</v>
@@ -1272,10 +1254,10 @@
         <v>21000</v>
       </c>
       <c r="N8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="O8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1305,7 +1287,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1316,13 +1298,13 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F9">
         <v>5800000</v>
@@ -1349,10 +1331,10 @@
         <v>2000</v>
       </c>
       <c r="N9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="O9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1382,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1393,13 +1375,13 @@
         <v>30</v>
       </c>
       <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
         <v>48</v>
       </c>
-      <c r="D10" t="s">
-        <v>50</v>
-      </c>
       <c r="E10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F10">
         <v>1400000</v>
@@ -1426,10 +1408,10 @@
         <v>16000</v>
       </c>
       <c r="N10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="O10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="P10">
         <v>72895458363</v>
@@ -1459,7 +1441,7 @@
         <v>-3801868433</v>
       </c>
       <c r="Y10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1467,16 +1449,16 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F11">
         <v>2234000</v>
@@ -1503,10 +1485,10 @@
         <v>10000</v>
       </c>
       <c r="N11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="O11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="P11">
         <v>1337894447</v>
@@ -1536,7 +1518,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y11" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1544,99 +1526,99 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F12">
-        <v>1350000</v>
+        <v>6000000</v>
       </c>
       <c r="G12">
-        <v>1350000</v>
+        <v>6000000</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>14000</v>
+        <v>2000</v>
       </c>
       <c r="J12">
-        <v>17000</v>
+        <v>2000</v>
       </c>
       <c r="K12">
-        <v>6471740</v>
+        <v>6345000</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>22000</v>
+        <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="O12" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P12">
-        <v>5214628820</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>6009352447</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>965797975</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>2015081728</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>1319755337</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>-44547594</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1503069100</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1410469786</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>24178632</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F13">
-        <v>6000000</v>
+        <v>4000000</v>
       </c>
       <c r="G13">
-        <v>6000000</v>
+        <v>4000000</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -1648,7 +1630,7 @@
         <v>2000</v>
       </c>
       <c r="K13">
-        <v>6345000</v>
+        <v>4420000</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1657,10 +1639,10 @@
         <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="O13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1690,84 +1672,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25">
-      <c r="A14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" t="s">
-        <v>71</v>
-      </c>
-      <c r="F14">
-        <v>4000000</v>
-      </c>
-      <c r="G14">
-        <v>4000000</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>2000</v>
-      </c>
-      <c r="J14">
-        <v>2000</v>
-      </c>
-      <c r="K14">
-        <v>4420000</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>2000</v>
-      </c>
-      <c r="N14" t="s">
-        <v>84</v>
-      </c>
-      <c r="O14" t="s">
-        <v>85</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet1.xlsx
+++ b/datasets/sheet1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="96">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -202,9 +202,6 @@
     <t>케이쓰리아이</t>
   </si>
   <si>
-    <t>넥스트바이오메디컬</t>
-  </si>
-  <si>
     <t>유라클</t>
   </si>
   <si>
@@ -238,9 +235,6 @@
     <t>239.23:1</t>
   </si>
   <si>
-    <t>356.95:1</t>
-  </si>
-  <si>
     <t>1065.86:1</t>
   </si>
   <si>
@@ -271,9 +265,6 @@
     <t>1.03%</t>
   </si>
   <si>
-    <t>2.18%</t>
-  </si>
-  <si>
     <t>0.55%</t>
   </si>
   <si>
@@ -296,9 +287,6 @@
   </si>
   <si>
     <t>XR 실감형콘텐츠</t>
-  </si>
-  <si>
-    <t>내시경용 지혈재, 혈관색전 미립구</t>
   </si>
   <si>
     <t>모바일 앱 개발 플랫폼</t>
@@ -671,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y13"/>
+  <dimension ref="A1:Y12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -792,10 +780,10 @@
         <v>2000</v>
       </c>
       <c r="N2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -825,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="Y2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -869,10 +857,10 @@
         <v>15300</v>
       </c>
       <c r="N3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P3">
         <v>7367362</v>
@@ -902,7 +890,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -946,10 +934,10 @@
         <v>13000</v>
       </c>
       <c r="N4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P4">
         <v>25588</v>
@@ -979,7 +967,7 @@
         <v>809</v>
       </c>
       <c r="Y4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1023,10 +1011,10 @@
         <v>2000</v>
       </c>
       <c r="N5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1056,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="Y5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1100,10 +1088,10 @@
         <v>15500</v>
       </c>
       <c r="N6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="P6">
         <v>10740898602</v>
@@ -1133,7 +1121,7 @@
         <v>219774608</v>
       </c>
       <c r="Y6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1144,43 +1132,43 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
         <v>62</v>
       </c>
       <c r="F7">
-        <v>1000000</v>
+        <v>751000</v>
       </c>
       <c r="G7">
-        <v>1000000</v>
+        <v>203700</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>547300</v>
       </c>
       <c r="I7">
-        <v>24000</v>
+        <v>18000</v>
       </c>
       <c r="J7">
-        <v>29000</v>
+        <v>21000</v>
       </c>
       <c r="K7">
-        <v>8008066</v>
+        <v>4330068</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>29000</v>
+        <v>21000</v>
       </c>
       <c r="N7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1210,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1218,307 +1206,307 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
         <v>63</v>
       </c>
       <c r="F8">
-        <v>751000</v>
+        <v>5800000</v>
       </c>
       <c r="G8">
-        <v>203700</v>
+        <v>5800000</v>
       </c>
       <c r="H8">
-        <v>547300</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>18000</v>
+        <v>2000</v>
       </c>
       <c r="J8">
-        <v>21000</v>
+        <v>2000</v>
       </c>
       <c r="K8">
-        <v>4330068</v>
+        <v>6100000</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>21000</v>
+        <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O8" t="s">
+        <v>79</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="s">
         <v>86</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:25">
       <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
         <v>30</v>
       </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
         <v>64</v>
       </c>
       <c r="F9">
-        <v>5800000</v>
+        <v>1400000</v>
       </c>
       <c r="G9">
-        <v>5800000</v>
+        <v>1400000</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>2000</v>
+        <v>16000</v>
       </c>
       <c r="J9">
-        <v>2000</v>
+        <v>19000</v>
       </c>
       <c r="K9">
-        <v>6100000</v>
+        <v>10000988</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>2000</v>
+        <v>16000</v>
       </c>
       <c r="N9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>72895458363</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>72913766913</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>11230711680</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>-6524077412</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>-4556157069</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>-3633759729</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>-11528915410</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>-7978634776</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>-3801868433</v>
       </c>
       <c r="Y9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:25">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
         <v>65</v>
       </c>
       <c r="F10">
-        <v>1400000</v>
+        <v>2234000</v>
       </c>
       <c r="G10">
-        <v>1400000</v>
+        <v>2234000</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>16000</v>
+        <v>7300</v>
       </c>
       <c r="J10">
-        <v>19000</v>
+        <v>8500</v>
       </c>
       <c r="K10">
-        <v>10000988</v>
+        <v>14965620</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P10">
-        <v>72895458363</v>
+        <v>1337894447</v>
       </c>
       <c r="Q10">
-        <v>72913766913</v>
+        <v>4495088983</v>
       </c>
       <c r="R10">
-        <v>11230711680</v>
+        <v>99398351</v>
       </c>
       <c r="S10">
-        <v>-6524077412</v>
+        <v>-3330678562</v>
       </c>
       <c r="T10">
-        <v>-4556157069</v>
+        <v>-2905069801</v>
       </c>
       <c r="U10">
-        <v>-3633759729</v>
+        <v>-1314068310</v>
       </c>
       <c r="V10">
-        <v>-11528915410</v>
+        <v>-9735376868</v>
       </c>
       <c r="W10">
-        <v>-7978634776</v>
+        <v>-5043515600</v>
       </c>
       <c r="X10">
-        <v>-3801868433</v>
+        <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
         <v>66</v>
       </c>
       <c r="F11">
-        <v>2234000</v>
+        <v>6000000</v>
       </c>
       <c r="G11">
-        <v>2234000</v>
+        <v>6000000</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>7300</v>
+        <v>2000</v>
       </c>
       <c r="J11">
-        <v>8500</v>
+        <v>2000</v>
       </c>
       <c r="K11">
-        <v>14965620</v>
+        <v>6345000</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O11" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="P11">
-        <v>1337894447</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>4495088983</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>99398351</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>-3330678562</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>-2905069801</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>-1314068310</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>-9735376868</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>-5043515600</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>-1257080998</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1529,19 +1517,19 @@
         <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
         <v>67</v>
       </c>
       <c r="F12">
-        <v>6000000</v>
+        <v>4000000</v>
       </c>
       <c r="G12">
-        <v>6000000</v>
+        <v>4000000</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1553,7 +1541,7 @@
         <v>2000</v>
       </c>
       <c r="K12">
-        <v>6345000</v>
+        <v>4420000</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1562,11 +1550,11 @@
         <v>2000</v>
       </c>
       <c r="N12" t="s">
+        <v>78</v>
+      </c>
+      <c r="O12" t="s">
         <v>79</v>
       </c>
-      <c r="O12" t="s">
-        <v>81</v>
-      </c>
       <c r="P12">
         <v>0</v>
       </c>
@@ -1595,84 +1583,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
-      <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13">
-        <v>4000000</v>
-      </c>
-      <c r="G13">
-        <v>4000000</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>2000</v>
-      </c>
-      <c r="J13">
-        <v>2000</v>
-      </c>
-      <c r="K13">
-        <v>4420000</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>2000</v>
-      </c>
-      <c r="N13" t="s">
-        <v>80</v>
-      </c>
-      <c r="O13" t="s">
-        <v>81</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet1.xlsx
+++ b/datasets/sheet1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="100">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -91,6 +91,9 @@
     <t>주요제품</t>
   </si>
   <si>
+    <t>2024-07-29</t>
+  </si>
+  <si>
     <t>2024-08-26</t>
   </si>
   <si>
@@ -106,9 +109,6 @@
     <t>2024-07-30</t>
   </si>
   <si>
-    <t>2024-07-29</t>
-  </si>
-  <si>
     <t>2024-07-23</t>
   </si>
   <si>
@@ -133,6 +133,9 @@
     <t>2024-07-10</t>
   </si>
   <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
     <t>2024-09-11</t>
   </si>
   <si>
@@ -148,9 +151,6 @@
     <t>2024-08-20</t>
   </si>
   <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
     <t>2024-08-13</t>
   </si>
   <si>
@@ -160,6 +160,9 @@
     <t>2024-07-26</t>
   </si>
   <si>
+    <t>대신</t>
+  </si>
+  <si>
     <t>미래</t>
   </si>
   <si>
@@ -169,9 +172,6 @@
     <t>한국</t>
   </si>
   <si>
-    <t>대신</t>
-  </si>
-  <si>
     <t>하나</t>
   </si>
   <si>
@@ -187,6 +187,9 @@
     <t>SK</t>
   </si>
   <si>
+    <t>아이언디바이스</t>
+  </si>
+  <si>
     <t>미래에셋비전스팩7호</t>
   </si>
   <si>
@@ -220,6 +223,9 @@
     <t>SK증권제13호스팩</t>
   </si>
   <si>
+    <t>1152.85:1</t>
+  </si>
+  <si>
     <t>1051.62 :1</t>
   </si>
   <si>
@@ -253,6 +259,9 @@
     <t>1197.45:1</t>
   </si>
   <si>
+    <t>3.34%</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
@@ -272,6 +281,9 @@
   </si>
   <si>
     <t>0.49%</t>
+  </si>
+  <si>
+    <t>스마트폰용 오디오 앰프 반도체 Soc</t>
   </si>
   <si>
     <t>기업인수합병</t>
@@ -659,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Y13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -744,7 +756,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
         <v>39</v>
@@ -756,64 +768,64 @@
         <v>57</v>
       </c>
       <c r="F2">
-        <v>7950000</v>
+        <v>3000000</v>
       </c>
       <c r="G2">
-        <v>7950000</v>
+        <v>3000000</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>2000</v>
+        <v>4900</v>
       </c>
       <c r="J2">
-        <v>2000</v>
+        <v>5700</v>
       </c>
       <c r="K2">
-        <v>8215000</v>
+        <v>13653263</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="N2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>5436813</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>6232339</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2471281</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>-1510039</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>-3517400</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>-1015682</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>-3268622</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>-3926782</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>-801640</v>
       </c>
       <c r="Y2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -821,7 +833,7 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
         <v>40</v>
@@ -833,64 +845,64 @@
         <v>58</v>
       </c>
       <c r="F3">
-        <v>1566800</v>
+        <v>7950000</v>
       </c>
       <c r="G3">
-        <v>1566800</v>
+        <v>7950000</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>13600</v>
+        <v>2000</v>
       </c>
       <c r="J3">
-        <v>15300</v>
+        <v>2000</v>
       </c>
       <c r="K3">
-        <v>9349954</v>
+        <v>8215000</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>15300</v>
+        <v>2000</v>
       </c>
       <c r="N3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P3">
-        <v>7367362</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>10525887</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>1790340</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>-9315442</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>-11755057</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>-2929307</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>-45566953</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>-5053520</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>-2903334</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -898,7 +910,7 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
         <v>41</v>
@@ -910,64 +922,64 @@
         <v>59</v>
       </c>
       <c r="F4">
-        <v>1000000</v>
+        <v>1566800</v>
       </c>
       <c r="G4">
-        <v>500000</v>
+        <v>1566800</v>
       </c>
       <c r="H4">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>9500</v>
+        <v>13600</v>
       </c>
       <c r="J4">
-        <v>10700</v>
+        <v>15300</v>
       </c>
       <c r="K4">
-        <v>5530000</v>
+        <v>9349954</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>13000</v>
+        <v>15300</v>
       </c>
       <c r="N4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="P4">
-        <v>25588</v>
+        <v>7367362</v>
       </c>
       <c r="Q4">
-        <v>30049</v>
+        <v>10525887</v>
       </c>
       <c r="R4">
-        <v>7363</v>
+        <v>1790340</v>
       </c>
       <c r="S4">
-        <v>3780</v>
+        <v>-9315442</v>
       </c>
       <c r="T4">
-        <v>5016</v>
+        <v>-11755057</v>
       </c>
       <c r="U4">
-        <v>938</v>
+        <v>-2929307</v>
       </c>
       <c r="V4">
-        <v>3456</v>
+        <v>-45566953</v>
       </c>
       <c r="W4">
-        <v>4688</v>
+        <v>-5053520</v>
       </c>
       <c r="X4">
-        <v>809</v>
+        <v>-2903334</v>
       </c>
       <c r="Y4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -987,64 +999,64 @@
         <v>60</v>
       </c>
       <c r="F5">
-        <v>6500000</v>
+        <v>1000000</v>
       </c>
       <c r="G5">
-        <v>6500000</v>
+        <v>500000</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="I5">
-        <v>2000</v>
+        <v>9500</v>
       </c>
       <c r="J5">
-        <v>2000</v>
+        <v>10700</v>
       </c>
       <c r="K5">
-        <v>7910000</v>
+        <v>5530000</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="N5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O5" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>25588</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>30049</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>7363</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>3780</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>5016</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>938</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>3456</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>4688</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>809</v>
       </c>
       <c r="Y5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1052,76 +1064,76 @@
         <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
         <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
         <v>61</v>
       </c>
       <c r="F6">
-        <v>1400000</v>
+        <v>6500000</v>
       </c>
       <c r="G6">
-        <v>1400000</v>
+        <v>6500000</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>12500</v>
+        <v>2000</v>
       </c>
       <c r="J6">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="K6">
-        <v>7486442</v>
+        <v>7910000</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="N6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O6" t="s">
         <v>82</v>
       </c>
       <c r="P6">
-        <v>10740898602</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>13058877126</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>3506428302</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1748628548</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>1115790858</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>191527654</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1491084554</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1185231988</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>219774608</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1129,123 +1141,123 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
         <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
         <v>62</v>
       </c>
       <c r="F7">
-        <v>751000</v>
+        <v>1400000</v>
       </c>
       <c r="G7">
-        <v>203700</v>
+        <v>1400000</v>
       </c>
       <c r="H7">
-        <v>547300</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>18000</v>
+        <v>12500</v>
       </c>
       <c r="J7">
-        <v>21000</v>
+        <v>15500</v>
       </c>
       <c r="K7">
-        <v>4330068</v>
+        <v>7486442</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>21000</v>
+        <v>15500</v>
       </c>
       <c r="N7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>10740898602</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>13058877126</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>3506428302</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1748628548</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1115790858</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>191527654</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1491084554</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1185231988</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>219774608</v>
       </c>
       <c r="Y7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
         <v>63</v>
       </c>
       <c r="F8">
-        <v>5800000</v>
+        <v>751000</v>
       </c>
       <c r="G8">
-        <v>5800000</v>
+        <v>203700</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>547300</v>
       </c>
       <c r="I8">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="J8">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="K8">
-        <v>6100000</v>
+        <v>4330068</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="N8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O8" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1275,238 +1287,238 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
         <v>64</v>
       </c>
       <c r="F9">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="G9">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="J9">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="K9">
-        <v>10000988</v>
+        <v>6100000</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="P9">
-        <v>72895458363</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>72913766913</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>11230711680</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>-6524077412</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>-4556157069</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>-3633759729</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>-11528915410</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>-7978634776</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>-3801868433</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
         <v>65</v>
       </c>
       <c r="F10">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="G10">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J10">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K10">
-        <v>14965620</v>
+        <v>10000988</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P10">
-        <v>1337894447</v>
+        <v>72895458363</v>
       </c>
       <c r="Q10">
-        <v>4495088983</v>
+        <v>72913766913</v>
       </c>
       <c r="R10">
-        <v>99398351</v>
+        <v>11230711680</v>
       </c>
       <c r="S10">
-        <v>-3330678562</v>
+        <v>-6524077412</v>
       </c>
       <c r="T10">
-        <v>-2905069801</v>
+        <v>-4556157069</v>
       </c>
       <c r="U10">
-        <v>-1314068310</v>
+        <v>-3633759729</v>
       </c>
       <c r="V10">
-        <v>-9735376868</v>
+        <v>-11528915410</v>
       </c>
       <c r="W10">
-        <v>-5043515600</v>
+        <v>-7978634776</v>
       </c>
       <c r="X10">
-        <v>-1257080998</v>
+        <v>-3801868433</v>
       </c>
       <c r="Y10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
         <v>66</v>
       </c>
       <c r="F11">
-        <v>6000000</v>
+        <v>2234000</v>
       </c>
       <c r="G11">
-        <v>6000000</v>
+        <v>2234000</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>2000</v>
+        <v>7300</v>
       </c>
       <c r="J11">
-        <v>2000</v>
+        <v>8500</v>
       </c>
       <c r="K11">
-        <v>6345000</v>
+        <v>14965620</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="N11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O11" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>1337894447</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>4495088983</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>99398351</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>-3330678562</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>-2905069801</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>-1314068310</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>-9735376868</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>-5043515600</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>-1257080998</v>
       </c>
       <c r="Y11" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1517,19 +1529,19 @@
         <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
         <v>67</v>
       </c>
       <c r="F12">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="G12">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1541,7 +1553,7 @@
         <v>2000</v>
       </c>
       <c r="K12">
-        <v>4420000</v>
+        <v>6345000</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1550,10 +1562,10 @@
         <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1583,7 +1595,84 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>95</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13">
+        <v>4000000</v>
+      </c>
+      <c r="G13">
+        <v>4000000</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>2000</v>
+      </c>
+      <c r="J13">
+        <v>2000</v>
+      </c>
+      <c r="K13">
+        <v>4420000</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>2000</v>
+      </c>
+      <c r="N13" t="s">
+        <v>80</v>
+      </c>
+      <c r="O13" t="s">
+        <v>82</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet1.xlsx
+++ b/datasets/sheet1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="90">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -109,9 +109,6 @@
     <t>2024-07-30</t>
   </si>
   <si>
-    <t>2024-07-23</t>
-  </si>
-  <si>
     <t>2024-07-15</t>
   </si>
   <si>
@@ -154,9 +151,6 @@
     <t>2024-08-13</t>
   </si>
   <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
     <t>2024-07-26</t>
   </si>
   <si>
@@ -184,9 +178,6 @@
     <t>삼성</t>
   </si>
   <si>
-    <t>SK</t>
-  </si>
-  <si>
     <t>아이언디바이스</t>
   </si>
   <si>
@@ -211,18 +202,12 @@
     <t>교보16호스팩</t>
   </si>
   <si>
-    <t>뱅크웨어글로벌</t>
-  </si>
-  <si>
     <t>아이빔테크놀로지</t>
   </si>
   <si>
     <t>엔에이치스팩31호</t>
   </si>
   <si>
-    <t>SK증권제13호스팩</t>
-  </si>
-  <si>
     <t>1152.85:1</t>
   </si>
   <si>
@@ -247,18 +232,12 @@
     <t>1085.71:1</t>
   </si>
   <si>
-    <t>155.74:1</t>
-  </si>
-  <si>
     <t>1011.50:1</t>
   </si>
   <si>
     <t>1123.43 :1</t>
   </si>
   <si>
-    <t>1197.45:1</t>
-  </si>
-  <si>
     <t>3.34%</t>
   </si>
   <si>
@@ -277,9 +256,6 @@
     <t>0.55%</t>
   </si>
   <si>
-    <t>1.52%</t>
-  </si>
-  <si>
     <t>0.49%</t>
   </si>
   <si>
@@ -304,16 +280,10 @@
     <t>모바일 앱 개발 플랫폼</t>
   </si>
   <si>
-    <t>국내외 은행 및 금융기업 대상 코어뱅킹 소프트웨어</t>
-  </si>
-  <si>
     <t>생체현미경, CRO 서비스</t>
   </si>
   <si>
     <t>금융지원서비스업</t>
-  </si>
-  <si>
-    <t>기업인수목적 주식회사</t>
   </si>
 </sst>
 </file>
@@ -671,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y13"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -759,13 +729,13 @@
         <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F2">
         <v>3000000</v>
@@ -792,10 +762,10 @@
         <v>7000</v>
       </c>
       <c r="N2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="O2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="P2">
         <v>5436813</v>
@@ -825,7 +795,7 @@
         <v>-801640</v>
       </c>
       <c r="Y2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -833,16 +803,16 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F3">
         <v>7950000</v>
@@ -869,40 +839,40 @@
         <v>2000</v>
       </c>
       <c r="N3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O3" t="s">
+        <v>75</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="s">
         <v>82</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -910,16 +880,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F4">
         <v>1566800</v>
@@ -946,10 +916,10 @@
         <v>15300</v>
       </c>
       <c r="N4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="O4" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="P4">
         <v>7367362</v>
@@ -979,7 +949,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y4" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -987,16 +957,16 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F5">
         <v>1000000</v>
@@ -1023,10 +993,10 @@
         <v>13000</v>
       </c>
       <c r="N5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="O5" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="P5">
         <v>25588</v>
@@ -1056,7 +1026,7 @@
         <v>809</v>
       </c>
       <c r="Y5" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1064,16 +1034,16 @@
         <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F6">
         <v>6500000</v>
@@ -1100,10 +1070,10 @@
         <v>2000</v>
       </c>
       <c r="N6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="O6" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1133,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1144,13 +1114,13 @@
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F7">
         <v>1400000</v>
@@ -1177,40 +1147,40 @@
         <v>15500</v>
       </c>
       <c r="N7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="O7" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="P7">
-        <v>10740898602</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>13058877126</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>3506428302</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>1748628548</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>1115790858</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>191527654</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>1491084554</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>1185231988</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>219774608</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1221,13 +1191,13 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F8">
         <v>751000</v>
@@ -1254,10 +1224,10 @@
         <v>21000</v>
       </c>
       <c r="N8" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O8" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1287,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1298,13 +1268,13 @@
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F9">
         <v>5800000</v>
@@ -1331,40 +1301,40 @@
         <v>2000</v>
       </c>
       <c r="N9" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="O9" t="s">
+        <v>75</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="s">
         <v>82</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1372,76 +1342,76 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F10">
-        <v>1400000</v>
+        <v>2234000</v>
       </c>
       <c r="G10">
-        <v>1400000</v>
+        <v>2234000</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>16000</v>
+        <v>7300</v>
       </c>
       <c r="J10">
-        <v>19000</v>
+        <v>8500</v>
       </c>
       <c r="K10">
-        <v>10000988</v>
+        <v>14965620</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="O10" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="P10">
-        <v>72895458363</v>
+        <v>1337894447</v>
       </c>
       <c r="Q10">
-        <v>72913766913</v>
+        <v>4495088983</v>
       </c>
       <c r="R10">
-        <v>11230711680</v>
+        <v>99398351</v>
       </c>
       <c r="S10">
-        <v>-6524077412</v>
+        <v>-3330678562</v>
       </c>
       <c r="T10">
-        <v>-4556157069</v>
+        <v>-2905069801</v>
       </c>
       <c r="U10">
-        <v>-3633759729</v>
+        <v>-1314068310</v>
       </c>
       <c r="V10">
-        <v>-11528915410</v>
+        <v>-9735376868</v>
       </c>
       <c r="W10">
-        <v>-7978634776</v>
+        <v>-5043515600</v>
       </c>
       <c r="X10">
-        <v>-3801868433</v>
+        <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1452,227 +1422,73 @@
         <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F11">
-        <v>2234000</v>
+        <v>6000000</v>
       </c>
       <c r="G11">
-        <v>2234000</v>
+        <v>6000000</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>7300</v>
+        <v>2000</v>
       </c>
       <c r="J11">
-        <v>8500</v>
+        <v>2000</v>
       </c>
       <c r="K11">
-        <v>14965620</v>
+        <v>6345000</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="O11" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="P11">
-        <v>1337894447</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>4495088983</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>99398351</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>-3330678562</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>-2905069801</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>-1314068310</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>-9735376868</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>-5043515600</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>-1257080998</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25">
-      <c r="A12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" t="s">
-        <v>67</v>
-      </c>
-      <c r="F12">
-        <v>6000000</v>
-      </c>
-      <c r="G12">
-        <v>6000000</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>2000</v>
-      </c>
-      <c r="J12">
-        <v>2000</v>
-      </c>
-      <c r="K12">
-        <v>6345000</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>2000</v>
-      </c>
-      <c r="N12" t="s">
-        <v>79</v>
-      </c>
-      <c r="O12" t="s">
-        <v>82</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
-      <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13">
-        <v>4000000</v>
-      </c>
-      <c r="G13">
-        <v>4000000</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>2000</v>
-      </c>
-      <c r="J13">
-        <v>2000</v>
-      </c>
-      <c r="K13">
-        <v>4420000</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>2000</v>
-      </c>
-      <c r="N13" t="s">
-        <v>80</v>
-      </c>
-      <c r="O13" t="s">
-        <v>82</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet1.xlsx
+++ b/datasets/sheet1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="84">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -112,9 +112,6 @@
     <t>2024-07-15</t>
   </si>
   <si>
-    <t>2024-07-09</t>
-  </si>
-  <si>
     <t>2024-08-27</t>
   </si>
   <si>
@@ -127,9 +124,6 @@
     <t>2024-07-19</t>
   </si>
   <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
     <t>2024-08-16</t>
   </si>
   <si>
@@ -151,9 +145,6 @@
     <t>2024-08-13</t>
   </si>
   <si>
-    <t>2024-07-26</t>
-  </si>
-  <si>
     <t>대신</t>
   </si>
   <si>
@@ -205,9 +196,6 @@
     <t>아이빔테크놀로지</t>
   </si>
   <si>
-    <t>엔에이치스팩31호</t>
-  </si>
-  <si>
     <t>1152.85:1</t>
   </si>
   <si>
@@ -235,9 +223,6 @@
     <t>1011.50:1</t>
   </si>
   <si>
-    <t>1123.43 :1</t>
-  </si>
-  <si>
     <t>3.34%</t>
   </si>
   <si>
@@ -281,9 +266,6 @@
   </si>
   <si>
     <t>생체현미경, CRO 서비스</t>
-  </si>
-  <si>
-    <t>금융지원서비스업</t>
   </si>
 </sst>
 </file>
@@ -641,7 +623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -729,13 +711,13 @@
         <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F2">
         <v>3000000</v>
@@ -762,10 +744,10 @@
         <v>7000</v>
       </c>
       <c r="N2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="O2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="P2">
         <v>5436813</v>
@@ -795,7 +777,7 @@
         <v>-801640</v>
       </c>
       <c r="Y2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -803,16 +785,16 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F3">
         <v>7950000</v>
@@ -839,10 +821,10 @@
         <v>2000</v>
       </c>
       <c r="N3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="O3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -872,7 +854,7 @@
         <v>0</v>
       </c>
       <c r="Y3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -880,16 +862,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F4">
         <v>1566800</v>
@@ -916,10 +898,10 @@
         <v>15300</v>
       </c>
       <c r="N4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="O4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="P4">
         <v>7367362</v>
@@ -949,7 +931,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -957,16 +939,16 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F5">
         <v>1000000</v>
@@ -993,10 +975,10 @@
         <v>13000</v>
       </c>
       <c r="N5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="P5">
         <v>25588</v>
@@ -1026,7 +1008,7 @@
         <v>809</v>
       </c>
       <c r="Y5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1034,16 +1016,16 @@
         <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F6">
         <v>6500000</v>
@@ -1070,10 +1052,10 @@
         <v>2000</v>
       </c>
       <c r="N6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="O6" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1103,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1114,13 +1096,13 @@
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F7">
         <v>1400000</v>
@@ -1147,40 +1129,40 @@
         <v>15500</v>
       </c>
       <c r="N7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="O7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>10740898602</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>13058877126</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>3506428302</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1748628548</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1115790858</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>191527654</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1491084554</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1185231988</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>219774608</v>
       </c>
       <c r="Y7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1191,13 +1173,13 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F8">
         <v>751000</v>
@@ -1224,10 +1206,10 @@
         <v>21000</v>
       </c>
       <c r="N8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O8" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1257,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1268,13 +1250,13 @@
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F9">
         <v>5800000</v>
@@ -1301,10 +1283,10 @@
         <v>2000</v>
       </c>
       <c r="N9" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="O9" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1334,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1342,16 +1324,16 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F10">
         <v>2234000</v>
@@ -1378,10 +1360,10 @@
         <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O10" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="P10">
         <v>1337894447</v>
@@ -1411,84 +1393,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
-      <c r="A11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11">
-        <v>6000000</v>
-      </c>
-      <c r="G11">
-        <v>6000000</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>2000</v>
-      </c>
-      <c r="J11">
-        <v>2000</v>
-      </c>
-      <c r="K11">
-        <v>6345000</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>2000</v>
-      </c>
-      <c r="N11" t="s">
-        <v>73</v>
-      </c>
-      <c r="O11" t="s">
-        <v>75</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet1.xlsx
+++ b/datasets/sheet1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="90">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -91,6 +91,9 @@
     <t>주요제품</t>
   </si>
   <si>
+    <t>2024-09-05</t>
+  </si>
+  <si>
     <t>2024-07-29</t>
   </si>
   <si>
@@ -112,6 +115,9 @@
     <t>2024-07-15</t>
   </si>
   <si>
+    <t>2024-09-06</t>
+  </si>
+  <si>
     <t>2024-08-27</t>
   </si>
   <si>
@@ -124,6 +130,9 @@
     <t>2024-07-19</t>
   </si>
   <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
     <t>2024-08-16</t>
   </si>
   <si>
@@ -145,6 +154,9 @@
     <t>2024-08-13</t>
   </si>
   <si>
+    <t>KB</t>
+  </si>
+  <si>
     <t>대신</t>
   </si>
   <si>
@@ -169,6 +181,9 @@
     <t>삼성</t>
   </si>
   <si>
+    <t>KB제30호스팩</t>
+  </si>
+  <si>
     <t>아이언디바이스</t>
   </si>
   <si>
@@ -196,6 +211,9 @@
     <t>아이빔테크놀로지</t>
   </si>
   <si>
+    <t>1217.75:1</t>
+  </si>
+  <si>
     <t>1152.85:1</t>
   </si>
   <si>
@@ -223,12 +241,12 @@
     <t>1011.50:1</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>3.34%</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>0.24%</t>
   </si>
   <si>
@@ -244,10 +262,10 @@
     <t>0.49%</t>
   </si>
   <si>
+    <t>기업인수합병</t>
+  </si>
+  <si>
     <t>스마트폰용 오디오 앰프 반도체 Soc</t>
-  </si>
-  <si>
-    <t>기업인수합병</t>
   </si>
   <si>
     <t>첨단바이오의약품 위탁개발생산(CDMO) 서비스 / 차세대 세포,유전자 치료제</t>
@@ -623,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -708,76 +726,76 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F2">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="G2">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>4900</v>
+        <v>2000</v>
       </c>
       <c r="J2">
-        <v>5700</v>
+        <v>2000</v>
       </c>
       <c r="K2">
-        <v>13653263</v>
+        <v>5310000</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>7000</v>
+        <v>2000</v>
       </c>
       <c r="N2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="O2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="P2">
-        <v>5436813</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>6232339</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>2471281</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>-1510039</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>-3517400</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>-1015682</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>-3268622</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>-3926782</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>-801640</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -785,76 +803,76 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F3">
-        <v>7950000</v>
+        <v>3000000</v>
       </c>
       <c r="G3">
-        <v>7950000</v>
+        <v>3000000</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>2000</v>
+        <v>4900</v>
       </c>
       <c r="J3">
-        <v>2000</v>
+        <v>5700</v>
       </c>
       <c r="K3">
-        <v>8215000</v>
+        <v>13653263</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="N3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="O3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>5436813</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>6232339</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2471281</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>-1510039</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>-3517400</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>-1015682</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>-3268622</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>-3926782</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>-801640</v>
       </c>
       <c r="Y3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -862,76 +880,76 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F4">
-        <v>1566800</v>
+        <v>7950000</v>
       </c>
       <c r="G4">
-        <v>1566800</v>
+        <v>7950000</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>13600</v>
+        <v>2000</v>
       </c>
       <c r="J4">
-        <v>15300</v>
+        <v>2000</v>
       </c>
       <c r="K4">
-        <v>9349954</v>
+        <v>8215000</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>15300</v>
+        <v>2000</v>
       </c>
       <c r="N4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="O4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="P4">
-        <v>7367362</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>10525887</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>1790340</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>-9315442</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>-11755057</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>-2929307</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>-45566953</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>-5053520</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>-2903334</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -939,76 +957,76 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F5">
-        <v>1000000</v>
+        <v>1566800</v>
       </c>
       <c r="G5">
-        <v>500000</v>
+        <v>1566800</v>
       </c>
       <c r="H5">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>9500</v>
+        <v>13600</v>
       </c>
       <c r="J5">
-        <v>10700</v>
+        <v>15300</v>
       </c>
       <c r="K5">
-        <v>5530000</v>
+        <v>9349954</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>13000</v>
+        <v>15300</v>
       </c>
       <c r="N5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="O5" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="P5">
-        <v>25588</v>
+        <v>7367362</v>
       </c>
       <c r="Q5">
-        <v>30049</v>
+        <v>10525887</v>
       </c>
       <c r="R5">
-        <v>7363</v>
+        <v>1790340</v>
       </c>
       <c r="S5">
-        <v>3780</v>
+        <v>-9315442</v>
       </c>
       <c r="T5">
-        <v>5016</v>
+        <v>-11755057</v>
       </c>
       <c r="U5">
-        <v>938</v>
+        <v>-2929307</v>
       </c>
       <c r="V5">
-        <v>3456</v>
+        <v>-45566953</v>
       </c>
       <c r="W5">
-        <v>4688</v>
+        <v>-5053520</v>
       </c>
       <c r="X5">
-        <v>809</v>
+        <v>-2903334</v>
       </c>
       <c r="Y5" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1016,76 +1034,76 @@
         <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F6">
-        <v>6500000</v>
+        <v>1000000</v>
       </c>
       <c r="G6">
-        <v>6500000</v>
+        <v>500000</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="I6">
-        <v>2000</v>
+        <v>9500</v>
       </c>
       <c r="J6">
-        <v>2000</v>
+        <v>10700</v>
       </c>
       <c r="K6">
-        <v>7910000</v>
+        <v>5530000</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="N6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="O6" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>25588</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>30049</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>7363</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>3780</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>5016</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>938</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>3456</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>4688</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>809</v>
       </c>
       <c r="Y6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1093,200 +1111,200 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
         <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F7">
-        <v>1400000</v>
+        <v>6500000</v>
       </c>
       <c r="G7">
-        <v>1400000</v>
+        <v>6500000</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>12500</v>
+        <v>2000</v>
       </c>
       <c r="J7">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="K7">
-        <v>7486442</v>
+        <v>7910000</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="N7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="O7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P7">
-        <v>10740898602</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>13058877126</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>3506428302</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>1748628548</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>1115790858</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>191527654</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>1491084554</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>1185231988</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>219774608</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F8">
-        <v>751000</v>
+        <v>1400000</v>
       </c>
       <c r="G8">
-        <v>203700</v>
+        <v>1400000</v>
       </c>
       <c r="H8">
-        <v>547300</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>18000</v>
+        <v>12500</v>
       </c>
       <c r="J8">
-        <v>21000</v>
+        <v>15500</v>
       </c>
       <c r="K8">
-        <v>4330068</v>
+        <v>7486442</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>21000</v>
+        <v>15500</v>
       </c>
       <c r="N8" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="O8" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>10740898602</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>13058877126</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>3506428302</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1748628548</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1115790858</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>191527654</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1491084554</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1185231988</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>219774608</v>
       </c>
       <c r="Y8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F9">
-        <v>5800000</v>
+        <v>751000</v>
       </c>
       <c r="G9">
-        <v>5800000</v>
+        <v>203700</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>547300</v>
       </c>
       <c r="I9">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="J9">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="K9">
-        <v>6100000</v>
+        <v>4330068</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="N9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="O9" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1316,84 +1334,161 @@
         <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:25">
       <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
         <v>31</v>
       </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F10">
-        <v>2234000</v>
+        <v>5800000</v>
       </c>
       <c r="G10">
-        <v>2234000</v>
+        <v>5800000</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>7300</v>
+        <v>2000</v>
       </c>
       <c r="J10">
-        <v>8500</v>
+        <v>2000</v>
       </c>
       <c r="K10">
-        <v>14965620</v>
+        <v>6100000</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N10" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="O10" t="s">
         <v>75</v>
       </c>
       <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11">
+        <v>2234000</v>
+      </c>
+      <c r="G11">
+        <v>2234000</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>7300</v>
+      </c>
+      <c r="J11">
+        <v>8500</v>
+      </c>
+      <c r="K11">
+        <v>14965620</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>10000</v>
+      </c>
+      <c r="N11" t="s">
+        <v>74</v>
+      </c>
+      <c r="O11" t="s">
+        <v>81</v>
+      </c>
+      <c r="P11">
         <v>1337894447</v>
       </c>
-      <c r="Q10">
+      <c r="Q11">
         <v>4495088983</v>
       </c>
-      <c r="R10">
+      <c r="R11">
         <v>99398351</v>
       </c>
-      <c r="S10">
+      <c r="S11">
         <v>-3330678562</v>
       </c>
-      <c r="T10">
+      <c r="T11">
         <v>-2905069801</v>
       </c>
-      <c r="U10">
+      <c r="U11">
         <v>-1314068310</v>
       </c>
-      <c r="V10">
+      <c r="V11">
         <v>-9735376868</v>
       </c>
-      <c r="W10">
+      <c r="W11">
         <v>-5043515600</v>
       </c>
-      <c r="X10">
+      <c r="X11">
         <v>-1257080998</v>
       </c>
-      <c r="Y10" t="s">
-        <v>83</v>
+      <c r="Y11" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
